--- a/outputs/019facd3-bb17-7462-8504-0210c0919463/ShellStorm2_美术资产台账_v001.xlsx
+++ b/outputs/019facd3-bb17-7462-8504-0210c0919463/ShellStorm2_美术资产台账_v001.xlsx
@@ -2,14 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="R8012e6c98da341e0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="资产主表" sheetId="2" r:id="R2690ce1b18a4437b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="角色组件" sheetId="3" r:id="Ra74e98fe9d4b44de"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="动画与状态" sheetId="4" r:id="R0d1b316386cb4d6c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分类与编码" sheetId="5" r:id="Rde2f7627bc9f4bdf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="命名与查重" sheetId="6" r:id="R05aaa99b8eed4ce5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="原型角色" sheetId="7" r:id="R9ed6945929714d85"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="版本记录" sheetId="8" r:id="Rd87daef3738f4d84"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="R289b0b33dc3648ca"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="资产主表" sheetId="2" r:id="Rf15988e7e2de435d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="角色组件" sheetId="3" r:id="R5ad4a732e89b495b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="动画与状态" sheetId="4" r:id="Raaa80265dbc8422b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分类与编码" sheetId="5" r:id="R6c1a7669ab9946ad"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="命名与查重" sheetId="6" r:id="Rdc70a16280ca40b8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="原型角色" sheetId="7" r:id="Reb5f700f84524e72"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="版本记录" sheetId="8" r:id="R0701514351e147cc"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -319,7 +319,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="96">
+  <x:cellXfs count="104">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -527,6 +527,30 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="22" fillId="22" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="18" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="20" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="20" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -900,7 +924,7 @@
       <x:c r="D6" s="43"/>
       <x:c r="E6" s="45" t="n">
         <x:f>COUNTIF('资产主表'!$K$6:$K$200,"待制作")+COUNTIF('资产主表'!$K$6:$K$200,"程序占位")</x:f>
-        <x:v>96</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="F6" s="43"/>
       <x:c r="G6" s="45" t="n">
@@ -1067,11 +1091,11 @@
       </x:c>
       <x:c r="B14" s="52" t="n">
         <x:f>COUNTIF('资产主表'!$C$6:$C$200,A14)</x:f>
-        <x:v>29</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C14" s="52" t="n">
         <x:f>COUNTIFS('资产主表'!$C$6:$C$200,A14,'资产主表'!$K$6:$K$200,"已完成")+COUNTIFS('资产主表'!$C$6:$C$200,A14,'资产主表'!$K$6:$K$200,"原型已接入")</x:f>
-        <x:v>10</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D14" s="43"/>
       <x:c r="E14" s="51" t="str">
@@ -11950,611 +11974,1058 @@
         <x:v>方形猫角色3D脚部DIY变体；复用CHR-PLY-CAPSULE01-3D玩家根；方形主语言，TailStub为用户指定圆尾例外；自动与视觉验收PASS</x:v>
       </x:c>
     </x:row>
-    <x:row r="156" ht="88" customHeight="1">
-      <x:c r="A156" s="63" t="str">
+    <x:row r="156" ht="132" customHeight="1">
+      <x:c r="A156" s="70" t="str">
         <x:v>CHR-PLY-CAPSULE01-3D-BUNNY01</x:v>
       </x:c>
-      <x:c r="B156" s="63" t="str">
+      <x:c r="B156" s="70" t="str">
         <x:v>兔子主角3D根变体</x:v>
       </x:c>
-      <x:c r="C156" s="63" t="str">
+      <x:c r="C156" s="70" t="str">
         <x:v>角色</x:v>
       </x:c>
-      <x:c r="D156" s="63" t="str">
+      <x:c r="D156" s="70" t="str">
         <x:v>player_variant</x:v>
       </x:c>
-      <x:c r="E156" s="63" t="str">
+      <x:c r="E156" s="70" t="str">
         <x:v>player_capsule01</x:v>
       </x:c>
-      <x:c r="F156" s="63" t="str">
+      <x:c r="F156" s="70" t="str">
         <x:v>root_3d_bunny01</x:v>
       </x:c>
-      <x:c r="G156" s="63" t="str">
+      <x:c r="G156" s="70" t="str">
         <x:v>CHR-PLY-CAPSULE01-3D</x:v>
       </x:c>
-      <x:c r="H156" s="63" t="str">
+      <x:c r="H156" s="70" t="str">
         <x:v>俯视3D</x:v>
       </x:c>
-      <x:c r="I156" s="63" t="str">
+      <x:c r="I156" s="70" t="str">
         <x:v>default</x:v>
       </x:c>
-      <x:c r="J156" s="63" t="str">
+      <x:c r="J156" s="70" t="str">
         <x:v>3D玩家场景</x:v>
       </x:c>
-      <x:c r="K156" s="63" t="str">
+      <x:c r="K156" s="70" t="str">
         <x:v>原型已接入</x:v>
       </x:c>
-      <x:c r="L156" s="63" t="str">
+      <x:c r="L156" s="70" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="M156" s="63" t="str">
-        <x:v>v004</x:v>
-      </x:c>
-      <x:c r="N156" s="63" t="str">
-        <x:v>1.705×2.475×1.064 m</x:v>
-      </x:c>
-      <x:c r="O156" s="63" t="str">
-        <x:v>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/chr_player_capsule01_bunny01_root_top3d_v004.tscn</x:v>
-      </x:c>
-      <x:c r="P156" s="63" t="str">
-        <x:v>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/chr_player_capsule01_bunny01_top3d_v004.blend</x:v>
-      </x:c>
-      <x:c r="Q156" s="63" t="str">
+      <x:c r="M156" s="70" t="str">
+        <x:v>v006</x:v>
+      </x:c>
+      <x:c r="N156" s="70" t="str">
+        <x:v>1.034×1.500×0.645 m / 完整视觉含耳</x:v>
+      </x:c>
+      <x:c r="O156" s="70" t="str">
+        <x:v>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/chr_player_capsule01_bunny01_root_top3d_v006.tscn</x:v>
+      </x:c>
+      <x:c r="P156" s="70" t="str">
+        <x:v>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/chr_player_capsule01_bunny01_top3d_v006.blend</x:v>
+      </x:c>
+      <x:c r="Q156" s="70" t="str">
         <x:v>兔子;主角;兔耳;3D;Blender;bunny01</x:v>
       </x:c>
-      <x:c r="R156" s="63" t="str">
+      <x:c r="R156" s="70" t="str">
         <x:f>LOWER(TRIM(C156)&amp;"|"&amp;TRIM(D156)&amp;"|"&amp;TRIM(E156)&amp;"|"&amp;TRIM(F156)&amp;"|"&amp;TRIM(H156)&amp;"|"&amp;TRIM(I156))</x:f>
         <x:v>角色|player_variant|player_capsule01|root_3d_bunny01|俯视3d|default</x:v>
       </x:c>
-      <x:c r="S156" s="63" t="str">
+      <x:c r="S156" s="70" t="str">
         <x:f>IF(A156="","",IF(COUNTIF($R$6:$R$162,R156)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
-      <x:c r="T156" s="63" t="str">
-        <x:v>2c34f9d637b480321fc287cb9a72d8d5d633a3aa3976ff0fbb21d3d7c8f9e621</x:v>
-      </x:c>
-      <x:c r="U156" s="63" t="str">
+      <x:c r="T156" s="70" t="str">
+        <x:v>b88839fbe76eedddd48933ac1807867e7a4efbd683de36475215679d26e84998</x:v>
+      </x:c>
+      <x:c r="U156" s="70" t="str">
         <x:v>Codex</x:v>
       </x:c>
-      <x:c r="V156" s="63" t="str">
-        <x:v>2026-07-29</x:v>
-      </x:c>
-      <x:c r="W156" s="63" t="str">
+      <x:c r="V156" s="71" t="n">
+        <x:v>46233</x:v>
+      </x:c>
+      <x:c r="W156" s="70" t="str">
         <x:v>用户提供 Blender 源文件 / Codex 模块化拆分</x:v>
       </x:c>
-      <x:c r="X156" s="63" t="str">
-        <x:v>v004 行为契约修正（网格、源文件与 AssetID 不变）：手部圆环定义为近端手腕轴心，球体为远端手掌；手枪在角色右侧单手握持，长枪右手握把、左手托举；hold/run/fire/reload/charge 由武器姿势状态机分离，七种枪体使用数据化差异后坐。六态状态机既有 idle 现驱动约 2.38s 站立循环：呼吸挤压、慢速重心换脚、头部反向滞后、双耳错相与偶发耳弹，移动输入出现即退出，停止后恢复。模型层级零碰撞；Player3D 根节点使用不可见 BoxShape3D 0.86×1.80×0.72m，顶部 1.80m ≤ 无耳头顶 1.820592m。自动与视觉验收 PASS。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="157" ht="58" customHeight="1">
-      <x:c r="A157" s="63" t="str">
+      <x:c r="X156" s="70" t="str">
+        <x:v>PH43：继续复用v006 1.5m模型与稳定AssetID；Player3D玩法碰撞升级为高1.5m、半径0.34m的VirtualCollisionCapsule。顶层状态扩展为idle/moving/dashing/hurt/locked/falling/landing/dead；下落收腿、耳后扬与落地压缩/回弹均由既有刚性节点程序驱动，不新增GLB或贴图。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="157" ht="118" customHeight="1">
+      <x:c r="A157" s="70" t="str">
         <x:v>CHR-PLY-CAPSULE01-3D-BUNNY01-BODY</x:v>
       </x:c>
-      <x:c r="B157" s="63" t="str">
+      <x:c r="B157" s="70" t="str">
         <x:v>兔子主角3D身体</x:v>
       </x:c>
-      <x:c r="C157" s="63" t="str">
+      <x:c r="C157" s="70" t="str">
         <x:v>角色</x:v>
       </x:c>
-      <x:c r="D157" s="63" t="str">
+      <x:c r="D157" s="70" t="str">
         <x:v>player_component</x:v>
       </x:c>
-      <x:c r="E157" s="63" t="str">
+      <x:c r="E157" s="70" t="str">
         <x:v>player_capsule01</x:v>
       </x:c>
-      <x:c r="F157" s="63" t="str">
+      <x:c r="F157" s="70" t="str">
         <x:v>body_3d_bunny01</x:v>
       </x:c>
-      <x:c r="G157" s="63" t="str">
+      <x:c r="G157" s="70" t="str">
         <x:v>CHR-PLY-CAPSULE01-3D-BUNNY01</x:v>
       </x:c>
-      <x:c r="H157" s="63" t="str">
+      <x:c r="H157" s="70" t="str">
         <x:v>俯视3D</x:v>
       </x:c>
-      <x:c r="I157" s="63" t="str">
+      <x:c r="I157" s="70" t="str">
         <x:v>default</x:v>
       </x:c>
-      <x:c r="J157" s="63" t="str">
+      <x:c r="J157" s="70" t="str">
         <x:v>3D玩家场景</x:v>
       </x:c>
-      <x:c r="K157" s="63" t="str">
+      <x:c r="K157" s="70" t="str">
         <x:v>原型已接入</x:v>
       </x:c>
-      <x:c r="L157" s="63" t="str">
+      <x:c r="L157" s="70" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="M157" s="63" t="str">
-        <x:v>v004</x:v>
-      </x:c>
-      <x:c r="N157" s="63" t="str">
-        <x:v>GLB / 1,958 verts / pivot-local</x:v>
-      </x:c>
-      <x:c r="O157" s="63" t="str">
-        <x:v>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_player_capsule01_bunny01_body_top3d_v004.glb</x:v>
-      </x:c>
-      <x:c r="P157" s="63" t="str">
-        <x:v>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/chr_player_capsule01_bunny01_top3d_v004.blend</x:v>
-      </x:c>
-      <x:c r="Q157" s="63" t="str">
+      <x:c r="M157" s="70" t="str">
+        <x:v>v006</x:v>
+      </x:c>
+      <x:c r="N157" s="70" t="str">
+        <x:v>GLB / 1,958 verts / pivot-local / 1.5m总高比例</x:v>
+      </x:c>
+      <x:c r="O157" s="70" t="str">
+        <x:v>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_player_capsule01_bunny01_body_top3d_v006.glb</x:v>
+      </x:c>
+      <x:c r="P157" s="70" t="str">
+        <x:v>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/chr_player_capsule01_bunny01_top3d_v006.blend</x:v>
+      </x:c>
+      <x:c r="Q157" s="70" t="str">
         <x:v>兔子;身体;服装;body;bunny01</x:v>
       </x:c>
-      <x:c r="R157" s="63" t="str">
+      <x:c r="R157" s="70" t="str">
         <x:f>LOWER(TRIM(C157)&amp;"|"&amp;TRIM(D157)&amp;"|"&amp;TRIM(E157)&amp;"|"&amp;TRIM(F157)&amp;"|"&amp;TRIM(H157)&amp;"|"&amp;TRIM(I157))</x:f>
         <x:v>角色|player_component|player_capsule01|body_3d_bunny01|俯视3d|default</x:v>
       </x:c>
-      <x:c r="S157" s="63" t="str">
+      <x:c r="S157" s="70" t="str">
         <x:f>IF(A157="","",IF(COUNTIF($R$6:$R$162,R157)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
-      <x:c r="T157" s="63" t="str">
-        <x:v>632b9e9832d5fbd367d3b4682035732ec43cfc02b797cb4f09a309099c9e42c1</x:v>
-      </x:c>
-      <x:c r="U157" s="63" t="str">
+      <x:c r="T157" s="70" t="str">
+        <x:v>c574d76e0f19c1aaa4bee5f427a81028d7b3f0f50299f67b4dbf02a60fc5668d</x:v>
+      </x:c>
+      <x:c r="U157" s="70" t="str">
         <x:v>Codex</x:v>
       </x:c>
-      <x:c r="V157" s="63" t="str">
-        <x:v>2026-07-29</x:v>
-      </x:c>
-      <x:c r="W157" s="63" t="str">
+      <x:c r="V157" s="71" t="n">
+        <x:v>46233</x:v>
+      </x:c>
+      <x:c r="W157" s="70" t="str">
         <x:v>用户提供 Blender 源文件</x:v>
       </x:c>
-      <x:c r="X157" s="63" t="str">
-        <x:v>BunnyRig/BodyJoint；底部中心原点；支持呼吸、突进压缩、完整翻滚和受击挤压回弹。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="158" ht="58" customHeight="1">
-      <x:c r="A158" s="63" t="str">
+      <x:c r="X157" s="70" t="str">
+        <x:v>PH41 v006：身体网格与底部中心原点从v005等比放大1.5倍；Godot BodyJoint=(-0.000030,0.155022,-0.000635)。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="158" ht="118" customHeight="1">
+      <x:c r="A158" s="70" t="str">
         <x:v>CHR-PLY-CAPSULE01-3D-BUNNY01-HEAD</x:v>
       </x:c>
-      <x:c r="B158" s="63" t="str">
+      <x:c r="B158" s="70" t="str">
         <x:v>兔子主角3D头部</x:v>
       </x:c>
-      <x:c r="C158" s="63" t="str">
+      <x:c r="C158" s="70" t="str">
         <x:v>角色</x:v>
       </x:c>
-      <x:c r="D158" s="63" t="str">
+      <x:c r="D158" s="70" t="str">
         <x:v>player_component</x:v>
       </x:c>
-      <x:c r="E158" s="63" t="str">
+      <x:c r="E158" s="70" t="str">
         <x:v>player_capsule01</x:v>
       </x:c>
-      <x:c r="F158" s="63" t="str">
+      <x:c r="F158" s="70" t="str">
         <x:v>head_3d_bunny01</x:v>
       </x:c>
-      <x:c r="G158" s="63" t="str">
+      <x:c r="G158" s="70" t="str">
         <x:v>CHR-PLY-CAPSULE01-3D-BUNNY01</x:v>
       </x:c>
-      <x:c r="H158" s="63" t="str">
+      <x:c r="H158" s="70" t="str">
         <x:v>俯视3D</x:v>
       </x:c>
-      <x:c r="I158" s="63" t="str">
+      <x:c r="I158" s="70" t="str">
         <x:v>default</x:v>
       </x:c>
-      <x:c r="J158" s="63" t="str">
+      <x:c r="J158" s="70" t="str">
         <x:v>3D玩家场景</x:v>
       </x:c>
-      <x:c r="K158" s="63" t="str">
+      <x:c r="K158" s="70" t="str">
         <x:v>原型已接入</x:v>
       </x:c>
-      <x:c r="L158" s="63" t="str">
+      <x:c r="L158" s="70" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="M158" s="63" t="str">
-        <x:v>v004</x:v>
-      </x:c>
-      <x:c r="N158" s="63" t="str">
-        <x:v>GLB / 5,936 verts / pivot-local</x:v>
-      </x:c>
-      <x:c r="O158" s="63" t="str">
-        <x:v>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_player_capsule01_bunny01_head_top3d_v004.glb</x:v>
-      </x:c>
-      <x:c r="P158" s="63" t="str">
-        <x:v>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/chr_player_capsule01_bunny01_top3d_v004.blend</x:v>
-      </x:c>
-      <x:c r="Q158" s="63" t="str">
+      <x:c r="M158" s="70" t="str">
+        <x:v>v006</x:v>
+      </x:c>
+      <x:c r="N158" s="70" t="str">
+        <x:v>GLB / 5,936 verts / pivot-local / 头顶1.103390m</x:v>
+      </x:c>
+      <x:c r="O158" s="70" t="str">
+        <x:v>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_player_capsule01_bunny01_head_top3d_v006.glb</x:v>
+      </x:c>
+      <x:c r="P158" s="70" t="str">
+        <x:v>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/chr_player_capsule01_bunny01_top3d_v006.blend</x:v>
+      </x:c>
+      <x:c r="Q158" s="70" t="str">
         <x:v>兔子;头部;head;bunny01</x:v>
       </x:c>
-      <x:c r="R158" s="63" t="str">
+      <x:c r="R158" s="70" t="str">
         <x:f>LOWER(TRIM(C158)&amp;"|"&amp;TRIM(D158)&amp;"|"&amp;TRIM(E158)&amp;"|"&amp;TRIM(F158)&amp;"|"&amp;TRIM(H158)&amp;"|"&amp;TRIM(I158))</x:f>
         <x:v>角色|player_component|player_capsule01|head_3d_bunny01|俯视3d|default</x:v>
       </x:c>
-      <x:c r="S158" s="63" t="str">
+      <x:c r="S158" s="70" t="str">
         <x:f>IF(A158="","",IF(COUNTIF($R$6:$R$162,R158)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
-      <x:c r="T158" s="63" t="str">
-        <x:v>4255cfdc374dc97a75d3386444edbd8c523ca174b9fc32b5c5fe48b9aedb4d1c</x:v>
-      </x:c>
-      <x:c r="U158" s="63" t="str">
+      <x:c r="T158" s="70" t="str">
+        <x:v>b8db86c722bb2ae4d760b8219051f492251f6b9fa29882c8e32453b020973c24</x:v>
+      </x:c>
+      <x:c r="U158" s="70" t="str">
         <x:v>Codex</x:v>
       </x:c>
-      <x:c r="V158" s="63" t="str">
-        <x:v>2026-07-29</x:v>
-      </x:c>
-      <x:c r="W158" s="63" t="str">
+      <x:c r="V158" s="71" t="n">
+        <x:v>46233</x:v>
+      </x:c>
+      <x:c r="W158" s="70" t="str">
         <x:v>用户提供 Blender 源文件</x:v>
       </x:c>
-      <x:c r="X158" s="63" t="str">
-        <x:v>BunnyRig/HeadJoint；头部下沿中心原点；耳朵通过 Head 子挂点装配；受击时承担夸张甩头和过冲回正。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="159" ht="58" customHeight="1">
-      <x:c r="A159" s="63" t="str">
+      <x:c r="X158" s="70" t="str">
+        <x:v>PH41 v006：头部与下沿中心原点真实1.5倍；不含耳头顶1.103390m，完整双耳顶部1.500m。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="159" ht="118" customHeight="1">
+      <x:c r="A159" s="70" t="str">
         <x:v>CHR-PLY-CAPSULE01-3D-BUNNY01-EARS</x:v>
       </x:c>
-      <x:c r="B159" s="63" t="str">
+      <x:c r="B159" s="70" t="str">
         <x:v>兔子主角3D双耳配件</x:v>
       </x:c>
-      <x:c r="C159" s="63" t="str">
+      <x:c r="C159" s="70" t="str">
         <x:v>角色</x:v>
       </x:c>
-      <x:c r="D159" s="63" t="str">
+      <x:c r="D159" s="70" t="str">
         <x:v>player_accessory</x:v>
       </x:c>
-      <x:c r="E159" s="63" t="str">
+      <x:c r="E159" s="70" t="str">
         <x:v>player_capsule01</x:v>
       </x:c>
-      <x:c r="F159" s="63" t="str">
+      <x:c r="F159" s="70" t="str">
         <x:v>ears_3d_bunny01</x:v>
       </x:c>
-      <x:c r="G159" s="63" t="str">
+      <x:c r="G159" s="70" t="str">
         <x:v>CHR-PLY-CAPSULE01-3D-BUNNY01-HEAD</x:v>
       </x:c>
-      <x:c r="H159" s="63" t="str">
+      <x:c r="H159" s="70" t="str">
         <x:v>俯视3D</x:v>
       </x:c>
-      <x:c r="I159" s="63" t="str">
+      <x:c r="I159" s="70" t="str">
         <x:v>default</x:v>
       </x:c>
-      <x:c r="J159" s="63" t="str">
+      <x:c r="J159" s="70" t="str">
         <x:v>3D玩家场景</x:v>
       </x:c>
-      <x:c r="K159" s="63" t="str">
+      <x:c r="K159" s="70" t="str">
         <x:v>原型已接入</x:v>
       </x:c>
-      <x:c r="L159" s="63" t="str">
+      <x:c r="L159" s="70" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="M159" s="63" t="str">
-        <x:v>v004</x:v>
-      </x:c>
-      <x:c r="N159" s="63" t="str">
-        <x:v>单 GLB / 1,536 verts / pivot-local</x:v>
-      </x:c>
-      <x:c r="O159" s="63" t="str">
-        <x:v>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_player_capsule01_bunny01_ear_top3d_v004.glb</x:v>
-      </x:c>
-      <x:c r="P159" s="63" t="str">
-        <x:v>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/chr_player_capsule01_bunny01_top3d_v004.blend</x:v>
-      </x:c>
-      <x:c r="Q159" s="63" t="str">
+      <x:c r="M159" s="70" t="str">
+        <x:v>v006</x:v>
+      </x:c>
+      <x:c r="N159" s="70" t="str">
+        <x:v>单 GLB / 1,536 verts / pivot-local / 双实例</x:v>
+      </x:c>
+      <x:c r="O159" s="70" t="str">
+        <x:v>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_player_capsule01_bunny01_ear_top3d_v006.glb</x:v>
+      </x:c>
+      <x:c r="P159" s="70" t="str">
+        <x:v>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/chr_player_capsule01_bunny01_top3d_v006.blend</x:v>
+      </x:c>
+      <x:c r="Q159" s="70" t="str">
         <x:v>兔耳;耳朵;耳部配件;EarSocketL;EarSocketR;bunny01</x:v>
       </x:c>
-      <x:c r="R159" s="63" t="str">
+      <x:c r="R159" s="70" t="str">
         <x:f>LOWER(TRIM(C159)&amp;"|"&amp;TRIM(D159)&amp;"|"&amp;TRIM(E159)&amp;"|"&amp;TRIM(F159)&amp;"|"&amp;TRIM(H159)&amp;"|"&amp;TRIM(I159))</x:f>
         <x:v>角色|player_accessory|player_capsule01|ears_3d_bunny01|俯视3d|default</x:v>
       </x:c>
-      <x:c r="S159" s="63" t="str">
+      <x:c r="S159" s="70" t="str">
         <x:f>IF(A159="","",IF(COUNTIF($R$6:$R$162,R159)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
-      <x:c r="T159" s="63" t="str">
-        <x:v>c768ac511df6636ba66ca3153b06a5348bffd2e6bfeed0f49c922ada982393ef</x:v>
-      </x:c>
-      <x:c r="U159" s="63" t="str">
+      <x:c r="T159" s="70" t="str">
+        <x:v>ed3c7abe283166648fafb43373c1dc2222bf9134f3d7bb8e0ebd8d3a05242ebf</x:v>
+      </x:c>
+      <x:c r="U159" s="70" t="str">
         <x:v>Codex</x:v>
       </x:c>
-      <x:c r="V159" s="63" t="str">
-        <x:v>2026-07-29</x:v>
-      </x:c>
-      <x:c r="W159" s="63" t="str">
+      <x:c r="V159" s="71" t="n">
+        <x:v>46233</x:v>
+      </x:c>
+      <x:c r="W159" s="70" t="str">
         <x:v>用户提供 Blender 源文件</x:v>
       </x:c>
-      <x:c r="X159" s="63" t="str">
-        <x:v>单个语义右耳局部模型；Godot EarSocketR 直接复用，EarSocketL 运行时 -X 镜像；耳根原点用于后压、收耳和甩动。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="160" ht="72" customHeight="1">
-      <x:c r="A160" s="63" t="str">
+      <x:c r="X159" s="70" t="str">
+        <x:v>PH41 v006：耳朵网格与耳根原点真实1.5倍；左右挂点复用单资产，装配后最高点严格1.500m。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="160" ht="118" customHeight="1">
+      <x:c r="A160" s="70" t="str">
         <x:v>CHR-PLY-CAPSULE01-3D-BUNNY01-HAND</x:v>
       </x:c>
-      <x:c r="B160" s="63" t="str">
+      <x:c r="B160" s="70" t="str">
         <x:v>兔子主角3D双爪表现组件</x:v>
       </x:c>
-      <x:c r="C160" s="63" t="str">
+      <x:c r="C160" s="70" t="str">
         <x:v>角色</x:v>
       </x:c>
-      <x:c r="D160" s="63" t="str">
+      <x:c r="D160" s="70" t="str">
         <x:v>player_component</x:v>
       </x:c>
-      <x:c r="E160" s="63" t="str">
+      <x:c r="E160" s="70" t="str">
         <x:v>player_capsule01</x:v>
       </x:c>
-      <x:c r="F160" s="63" t="str">
+      <x:c r="F160" s="70" t="str">
         <x:v>hand_3d_bunny01</x:v>
       </x:c>
-      <x:c r="G160" s="63" t="str">
+      <x:c r="G160" s="70" t="str">
         <x:v>CHR-PLY-CAPSULE01-3D-BUNNY01</x:v>
       </x:c>
-      <x:c r="H160" s="63" t="str">
+      <x:c r="H160" s="70" t="str">
         <x:v>俯视3D</x:v>
       </x:c>
-      <x:c r="I160" s="63" t="str">
+      <x:c r="I160" s="70" t="str">
         <x:v>default</x:v>
       </x:c>
-      <x:c r="J160" s="63" t="str">
+      <x:c r="J160" s="70" t="str">
         <x:v>3D玩家场景</x:v>
       </x:c>
-      <x:c r="K160" s="63" t="str">
+      <x:c r="K160" s="70" t="str">
         <x:v>原型已接入</x:v>
       </x:c>
-      <x:c r="L160" s="63" t="str">
+      <x:c r="L160" s="70" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="M160" s="63" t="str">
-        <x:v>v004</x:v>
-      </x:c>
-      <x:c r="N160" s="63" t="str">
-        <x:v>双 GLB / 左右各 1,058 verts / pivot-local</x:v>
-      </x:c>
-      <x:c r="O160" s="63" t="str">
-        <x:v>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_player_capsule01_bunny01_hand_l_top3d_v004.glb; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_player_capsule01_bunny01_hand_r_top3d_v004.glb</x:v>
-      </x:c>
-      <x:c r="P160" s="63" t="str">
-        <x:v>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/chr_player_capsule01_bunny01_top3d_v004.blend</x:v>
-      </x:c>
-      <x:c r="Q160" s="63" t="str">
+      <x:c r="M160" s="70" t="str">
+        <x:v>v006</x:v>
+      </x:c>
+      <x:c r="N160" s="70" t="str">
+        <x:v>双 GLB / 左右各1,058 verts / pivot-local / 1.5m角色比例</x:v>
+      </x:c>
+      <x:c r="O160" s="70" t="str">
+        <x:v>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_player_capsule01_bunny01_hand_l_top3d_v006.glb; assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_player_capsule01_bunny01_hand_r_top3d_v006.glb</x:v>
+      </x:c>
+      <x:c r="P160" s="70" t="str">
+        <x:v>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/chr_player_capsule01_bunny01_top3d_v006.blend</x:v>
+      </x:c>
+      <x:c r="Q160" s="70" t="str">
         <x:v>兔爪;手;握持;weapon_socket;bunny01</x:v>
       </x:c>
-      <x:c r="R160" s="63" t="str">
+      <x:c r="R160" s="70" t="str">
         <x:f>LOWER(TRIM(C160)&amp;"|"&amp;TRIM(D160)&amp;"|"&amp;TRIM(E160)&amp;"|"&amp;TRIM(F160)&amp;"|"&amp;TRIM(H160)&amp;"|"&amp;TRIM(I160))</x:f>
         <x:v>角色|player_component|player_capsule01|hand_3d_bunny01|俯视3d|default</x:v>
       </x:c>
-      <x:c r="S160" s="63" t="str">
+      <x:c r="S160" s="70" t="str">
         <x:f>IF(A160="","",IF(COUNTIF($R$6:$R$162,R160)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
-      <x:c r="T160" s="63" t="str">
-        <x:v>6171ea35985b712446983d7c5fa27ae8c248e4516f487c709a302de6e845d088 / d421b98ded85d9580ad41189ab6fd3095f579447c1ef64ef659e87b6ec72581e</x:v>
-      </x:c>
-      <x:c r="U160" s="63" t="str">
+      <x:c r="T160" s="70" t="str">
+        <x:v>2c6647c0e4f234e9312ba65e7c73f55c02627be9b7a2c35d1591d86a20cb5f16 / b3ada7b67d0224156d1c39af0bdc0e53af02cb5d26ba68d4746b7859a84a1d10</x:v>
+      </x:c>
+      <x:c r="U160" s="70" t="str">
         <x:v>Codex</x:v>
       </x:c>
-      <x:c r="V160" s="63" t="str">
-        <x:v>2026-07-29</x:v>
-      </x:c>
-      <x:c r="W160" s="63" t="str">
+      <x:c r="V160" s="71" t="n">
+        <x:v>46233</x:v>
+      </x:c>
+      <x:c r="W160" s="70" t="str">
         <x:v>用户提供 Blender 源文件</x:v>
       </x:c>
-      <x:c r="X160" s="63" t="str">
-        <x:v>BunnyRig/HandRoot/HandJointL/R；圆环=近端手腕/动画轴心，球体=远端手掌。手枪仅右手握持且置于角色右侧，左手自由摆动；长枪右手握把、左手托举；跑步、射击、换弹、蓄力分别由武器姿势状态管理，手枪/霰弹/步枪/机枪/狙击/发射器/蓄力枪具备差异后坐参数。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="161" ht="58" customHeight="1">
-      <x:c r="A161" s="63" t="str">
+      <x:c r="X160" s="70" t="str">
+        <x:v>PH41 v006：左右手、手腕原点、单/双手握持目标和动作平移统一改用0.606060606米制比例；持枪外观与确认预览一致。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="161" ht="132" customHeight="1">
+      <x:c r="A161" s="70" t="str">
         <x:v>CHR-PLY-CAPSULE01-3D-BUNNY01-FOOT-L</x:v>
       </x:c>
-      <x:c r="B161" s="63" t="str">
+      <x:c r="B161" s="70" t="str">
         <x:v>兔子主角3D左脚</x:v>
       </x:c>
-      <x:c r="C161" s="63" t="str">
+      <x:c r="C161" s="70" t="str">
         <x:v>角色</x:v>
       </x:c>
-      <x:c r="D161" s="63" t="str">
+      <x:c r="D161" s="70" t="str">
         <x:v>player_component</x:v>
       </x:c>
-      <x:c r="E161" s="63" t="str">
+      <x:c r="E161" s="70" t="str">
         <x:v>player_capsule01</x:v>
       </x:c>
-      <x:c r="F161" s="63" t="str">
+      <x:c r="F161" s="70" t="str">
         <x:v>foot_l_3d_bunny01</x:v>
       </x:c>
-      <x:c r="G161" s="63" t="str">
+      <x:c r="G161" s="70" t="str">
         <x:v>CHR-PLY-CAPSULE01-3D-BUNNY01</x:v>
       </x:c>
-      <x:c r="H161" s="63" t="str">
+      <x:c r="H161" s="70" t="str">
         <x:v>俯视3D</x:v>
       </x:c>
-      <x:c r="I161" s="63" t="str">
+      <x:c r="I161" s="70" t="str">
         <x:v>moving</x:v>
       </x:c>
-      <x:c r="J161" s="63" t="str">
+      <x:c r="J161" s="70" t="str">
         <x:v>3D玩家场景</x:v>
       </x:c>
-      <x:c r="K161" s="63" t="str">
+      <x:c r="K161" s="70" t="str">
         <x:v>原型已接入</x:v>
       </x:c>
-      <x:c r="L161" s="63" t="str">
+      <x:c r="L161" s="70" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="M161" s="63" t="str">
-        <x:v>v004</x:v>
-      </x:c>
-      <x:c r="N161" s="63" t="str">
-        <x:v>GLB / 5,396 verts / pivot-local</x:v>
-      </x:c>
-      <x:c r="O161" s="63" t="str">
-        <x:v>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_player_capsule01_bunny01_foot_l_top3d_v004.glb</x:v>
-      </x:c>
-      <x:c r="P161" s="63" t="str">
-        <x:v>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/chr_player_capsule01_bunny01_top3d_v004.blend</x:v>
-      </x:c>
-      <x:c r="Q161" s="63" t="str">
+      <x:c r="M161" s="70" t="str">
+        <x:v>v006</x:v>
+      </x:c>
+      <x:c r="N161" s="70" t="str">
+        <x:v>GLB / 5,396 verts / pivot-local / 1.5m角色比例</x:v>
+      </x:c>
+      <x:c r="O161" s="70" t="str">
+        <x:v>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_player_capsule01_bunny01_foot_l_top3d_v006.glb</x:v>
+      </x:c>
+      <x:c r="P161" s="70" t="str">
+        <x:v>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/chr_player_capsule01_bunny01_top3d_v006.blend</x:v>
+      </x:c>
+      <x:c r="Q161" s="70" t="str">
         <x:v>兔脚;左脚;步态;FootL;bunny01</x:v>
       </x:c>
-      <x:c r="R161" s="63" t="str">
+      <x:c r="R161" s="70" t="str">
         <x:f>LOWER(TRIM(C161)&amp;"|"&amp;TRIM(D161)&amp;"|"&amp;TRIM(E161)&amp;"|"&amp;TRIM(F161)&amp;"|"&amp;TRIM(H161)&amp;"|"&amp;TRIM(I161))</x:f>
         <x:v>角色|player_component|player_capsule01|foot_l_3d_bunny01|俯视3d|moving</x:v>
       </x:c>
-      <x:c r="S161" s="63" t="str">
+      <x:c r="S161" s="70" t="str">
         <x:f>IF(A161="","",IF(COUNTIF($R$6:$R$162,R161)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
-      <x:c r="T161" s="63" t="str">
-        <x:v>ba37215c7a03dae202dd03c6b2151b179dae0bfca345142bf7b0bd6268203251</x:v>
-      </x:c>
-      <x:c r="U161" s="63" t="str">
+      <x:c r="T161" s="70" t="str">
+        <x:v>52051cba0db701d977c8baa8d7ed9899825b10406803ac63e6a3f66efbd80b64</x:v>
+      </x:c>
+      <x:c r="U161" s="70" t="str">
         <x:v>Codex</x:v>
       </x:c>
-      <x:c r="V161" s="63" t="str">
-        <x:v>2026-07-29</x:v>
-      </x:c>
-      <x:c r="W161" s="63" t="str">
+      <x:c r="V161" s="71" t="n">
+        <x:v>46233</x:v>
+      </x:c>
+      <x:c r="W161" s="70" t="str">
         <x:v>用户提供 Blender 源文件</x:v>
       </x:c>
-      <x:c r="X161" s="63" t="str">
-        <x:v>BunnyRig/FeetRoot/FootJointL；脚底中心原点；支持交替步态、翻滚收腿、受击甩脚和落地挤压。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="162" ht="58" customHeight="1">
-      <x:c r="A162" s="63" t="str">
+      <x:c r="X161" s="70" t="str">
+        <x:v>PH43：v006网格与AssetID不变；FootJointL除moving步态外新增falling收腿与landing压缩恢复职责，动作由PlayerAvatar3D程序变换驱动。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="162" ht="132" customHeight="1">
+      <x:c r="A162" s="70" t="str">
         <x:v>CHR-PLY-CAPSULE01-3D-BUNNY01-FOOT-R</x:v>
       </x:c>
-      <x:c r="B162" s="63" t="str">
+      <x:c r="B162" s="70" t="str">
         <x:v>兔子主角3D右脚</x:v>
       </x:c>
-      <x:c r="C162" s="63" t="str">
+      <x:c r="C162" s="70" t="str">
         <x:v>角色</x:v>
       </x:c>
-      <x:c r="D162" s="63" t="str">
+      <x:c r="D162" s="70" t="str">
         <x:v>player_component</x:v>
       </x:c>
-      <x:c r="E162" s="63" t="str">
+      <x:c r="E162" s="70" t="str">
         <x:v>player_capsule01</x:v>
       </x:c>
-      <x:c r="F162" s="63" t="str">
+      <x:c r="F162" s="70" t="str">
         <x:v>foot_r_3d_bunny01</x:v>
       </x:c>
-      <x:c r="G162" s="63" t="str">
+      <x:c r="G162" s="70" t="str">
         <x:v>CHR-PLY-CAPSULE01-3D-BUNNY01</x:v>
       </x:c>
-      <x:c r="H162" s="63" t="str">
+      <x:c r="H162" s="70" t="str">
         <x:v>俯视3D</x:v>
       </x:c>
-      <x:c r="I162" s="63" t="str">
+      <x:c r="I162" s="70" t="str">
         <x:v>moving</x:v>
       </x:c>
-      <x:c r="J162" s="63" t="str">
+      <x:c r="J162" s="70" t="str">
         <x:v>3D玩家场景</x:v>
       </x:c>
-      <x:c r="K162" s="63" t="str">
+      <x:c r="K162" s="70" t="str">
         <x:v>原型已接入</x:v>
       </x:c>
-      <x:c r="L162" s="63" t="str">
+      <x:c r="L162" s="70" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="M162" s="63" t="str">
-        <x:v>v004</x:v>
-      </x:c>
-      <x:c r="N162" s="63" t="str">
-        <x:v>GLB / 5,396 verts / pivot-local</x:v>
-      </x:c>
-      <x:c r="O162" s="63" t="str">
-        <x:v>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_player_capsule01_bunny01_foot_r_top3d_v004.glb</x:v>
-      </x:c>
-      <x:c r="P162" s="63" t="str">
-        <x:v>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/chr_player_capsule01_bunny01_top3d_v004.blend</x:v>
-      </x:c>
-      <x:c r="Q162" s="63" t="str">
+      <x:c r="M162" s="70" t="str">
+        <x:v>v006</x:v>
+      </x:c>
+      <x:c r="N162" s="70" t="str">
+        <x:v>GLB / 5,396 verts / pivot-local / 1.5m角色比例</x:v>
+      </x:c>
+      <x:c r="O162" s="70" t="str">
+        <x:v>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_player_capsule01_bunny01_foot_r_top3d_v006.glb</x:v>
+      </x:c>
+      <x:c r="P162" s="70" t="str">
+        <x:v>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/source/chr_player_capsule01_bunny01_top3d_v006.blend</x:v>
+      </x:c>
+      <x:c r="Q162" s="70" t="str">
         <x:v>兔脚;右脚;步态;FootR;bunny01</x:v>
       </x:c>
-      <x:c r="R162" s="63" t="str">
+      <x:c r="R162" s="70" t="str">
         <x:f>LOWER(TRIM(C162)&amp;"|"&amp;TRIM(D162)&amp;"|"&amp;TRIM(E162)&amp;"|"&amp;TRIM(F162)&amp;"|"&amp;TRIM(H162)&amp;"|"&amp;TRIM(I162))</x:f>
         <x:v>角色|player_component|player_capsule01|foot_r_3d_bunny01|俯视3d|moving</x:v>
       </x:c>
-      <x:c r="S162" s="63" t="str">
+      <x:c r="S162" s="70" t="str">
         <x:f>IF(A162="","",IF(COUNTIF($R$6:$R$162,R162)&gt;1,"重复","唯一"))</x:f>
         <x:v>唯一</x:v>
       </x:c>
-      <x:c r="T162" s="63" t="str">
-        <x:v>9afad545f5f7f1ffa13db7d33bb71ba6df913c9072b6b9a32d673f5c4b24438a</x:v>
-      </x:c>
-      <x:c r="U162" s="63" t="str">
+      <x:c r="T162" s="70" t="str">
+        <x:v>d81e840f5c087b349fd6e19b4cb7e65eb79294edb937fdc75192b66967c29e2e</x:v>
+      </x:c>
+      <x:c r="U162" s="70" t="str">
         <x:v>Codex</x:v>
       </x:c>
-      <x:c r="V162" s="63" t="str">
-        <x:v>2026-07-29</x:v>
-      </x:c>
-      <x:c r="W162" s="63" t="str">
+      <x:c r="V162" s="71" t="n">
+        <x:v>46233</x:v>
+      </x:c>
+      <x:c r="W162" s="70" t="str">
         <x:v>用户提供 Blender 源文件</x:v>
       </x:c>
-      <x:c r="X162" s="63" t="str">
-        <x:v>BunnyRig/FeetRoot/FootJointR；脚底中心原点；与左脚独立交替并参与翻滚/受击关键姿势。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="163">
-      <x:c r="A163" t="str">
+      <x:c r="X162" s="70" t="str">
+        <x:v>PH43：v006网格与AssetID不变；FootJointR除moving步态外新增falling收腿与landing压缩恢复职责，动作由PlayerAvatar3D程序变换驱动。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="163" ht="132" customHeight="1">
+      <x:c r="A163" s="70" t="str">
         <x:v>ENV-TOWER-DESCENT-KIT-3D</x:v>
       </x:c>
-      <x:c r="B163" t="str">
-        <x:v>向下爬楼塔楼3D模块化母版</x:v>
-      </x:c>
-      <x:c r="C163" t="str">
+      <x:c r="B163" s="70" t="str">
+        <x:v>向下爬楼塔楼3D五米模块化母版</x:v>
+      </x:c>
+      <x:c r="C163" s="70" t="str">
         <x:v>场景</x:v>
       </x:c>
-      <x:c r="D163" t="str">
+      <x:c r="D163" s="70" t="str">
         <x:v>room_kit</x:v>
       </x:c>
-      <x:c r="E163" t="str">
+      <x:c r="E163" s="70" t="str">
         <x:v>tower_descent</x:v>
       </x:c>
-      <x:c r="F163" t="str">
+      <x:c r="F163" s="70" t="str">
         <x:v>root_3d</x:v>
       </x:c>
-      <x:c r="G163" t="str">
+      <x:c r="G163" s="70" t="str">
         <x:v>ENV-DUNGEON-RUNTIME-3D</x:v>
       </x:c>
-      <x:c r="H163" t="str">
+      <x:c r="H163" s="70" t="str">
         <x:v>俯视3D</x:v>
       </x:c>
-      <x:c r="I163" t="str">
-        <x:v>blender_review</x:v>
-      </x:c>
-      <x:c r="J163" t="str">
-        <x:v>楼顶/设施层/五层战斗层/通用楼梯间</x:v>
-      </x:c>
-      <x:c r="K163" t="str">
-        <x:v>待制作</x:v>
-      </x:c>
-      <x:c r="L163" t="str">
+      <x:c r="I163" s="70" t="str">
+        <x:v>godot_runtime</x:v>
+      </x:c>
+      <x:c r="J163" s="70" t="str">
+        <x:v>335m楼顶/99层基地/98—95层种子化探索关卡/六个GLB运行时子资产</x:v>
+      </x:c>
+      <x:c r="K163" s="70" t="str">
+        <x:v>原型已接入</x:v>
+      </x:c>
+      <x:c r="L163" s="70" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="M163" t="str">
+      <x:c r="M163" s="70" t="str">
+        <x:v>v006</x:v>
+      </x:c>
+      <x:c r="N163" s="70" t="str">
+        <x:v>Blender 4.2源文件/1单位=1m/432对象/114 Mesh/18个未应用Array</x:v>
+      </x:c>
+      <x:c r="O163" s="70" t="str">
+        <x:v>assets/art/environments/tower_descent_3d/source/env_tower_descent_kit_top3d_v006.blend</x:v>
+      </x:c>
+      <x:c r="P163" s="70" t="str">
+        <x:v>env_tower_descent_kit_top3d_v006.blend; export_env_tower_5m_modules_v001.py; export_env_tower_stairwells_v001.py; docs/PH37_摩天楼99至95层深度玩法与楼梯资产接入.md; verify_tower_descent_flow.tscn</x:v>
+      </x:c>
+      <x:c r="Q163" s="70" t="str">
+        <x:v>塔楼;向下爬楼;楼顶;基地层;战斗层;特殊楼梯;通用楼梯;五米网格;模块化地砖;模块化墙;模块化门;Blender</x:v>
+      </x:c>
+      <x:c r="R163" s="70" t="str">
+        <x:v>场景|room_kit|tower_descent|root_3d|俯视3d|blender_review</x:v>
+      </x:c>
+      <x:c r="S163" s="70" t="str">
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T163" s="70" t="str">
+        <x:v>a99ca6f01c875cdf9414a9f132bbb9d4c2a921b4b4871346170ee6e6701130a2</x:v>
+      </x:c>
+      <x:c r="U163" s="70" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V163" s="71" t="n">
+        <x:v>46233</x:v>
+      </x:c>
+      <x:c r="W163" s="70" t="str">
+        <x:v>用户手工Blender楼梯 + Codex五米模块化楼层</x:v>
+      </x:c>
+      <x:c r="X163" s="70" t="str">
+        <x:v>PH44：Godot整层统一为50×50个5m网格，即250×250m、2500块地砖；65×65m基地核心保持不变，并以XZ各+2.5m对齐偶数整层网格。普通战斗层采用4×4槽位：12个45×45m外环房间，中央2×2槽位留给10m主走廊与上下楼梯。Boss层采用90×90m Boss区并保留9个普通房间。固定镜头仍为角色相对(0,8,5.5)、FOV 55°；新增仅隐藏镜头到角色射线所命中的墙体渲染的局部剖切，碰撞、门、视野阻挡与楼梯承重均不关闭。完整探索节点数2783。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="164" ht="132" customHeight="1">
+      <x:c r="A164" s="70" t="str">
+        <x:v>ENV-TOWER-FLOOR-TILE-5M</x:v>
+      </x:c>
+      <x:c r="B164" s="70" t="str">
+        <x:v>塔楼5米地砖模块</x:v>
+      </x:c>
+      <x:c r="C164" s="70" t="str">
+        <x:v>场景</x:v>
+      </x:c>
+      <x:c r="D164" s="70" t="str">
+        <x:v>room_kit</x:v>
+      </x:c>
+      <x:c r="E164" s="70" t="str">
+        <x:v>tower_descent</x:v>
+      </x:c>
+      <x:c r="F164" s="70" t="str">
+        <x:v>floor_tile_5m</x:v>
+      </x:c>
+      <x:c r="G164" s="70" t="str">
+        <x:v>ENV-TOWER-DESCENT-KIT-3D</x:v>
+      </x:c>
+      <x:c r="H164" s="70" t="str">
+        <x:v>俯视3D</x:v>
+      </x:c>
+      <x:c r="I164" s="70" t="str">
+        <x:v>godot_runtime</x:v>
+      </x:c>
+      <x:c r="J164" s="70" t="str">
+        <x:v>塔楼六个物理层楼板/335m MultiMesh网格</x:v>
+      </x:c>
+      <x:c r="K164" s="70" t="str">
+        <x:v>原型已接入</x:v>
+      </x:c>
+      <x:c r="L164" s="70" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="M164" s="70" t="str">
         <x:v>v001</x:v>
       </x:c>
-      <x:c r="N163" t="str">
-        <x:v>Blender 4.2源文件/1单位=1m/122 Mesh</x:v>
-      </x:c>
-      <x:c r="O163" t="str">
-        <x:v>assets/art/environments/tower_descent_3d/source/env_tower_descent_kit_top3d_v001.blend</x:v>
-      </x:c>
-      <x:c r="P163" t="str">
-        <x:v>待用户确认后导出components/*.glb并接入TowerDescent3D</x:v>
-      </x:c>
-      <x:c r="Q163" t="str">
-        <x:v>塔楼;向下爬楼;楼顶;基地层;战斗层;门口走道;折角走道;斜坡楼梯;Blender</x:v>
-      </x:c>
-      <x:c r="R163" t="str">
-        <x:f>LOWER(TRIM(C163)&amp;"|"&amp;TRIM(D163)&amp;"|"&amp;TRIM(E163)&amp;"|"&amp;TRIM(F163)&amp;"|"&amp;TRIM(H163)&amp;"|"&amp;TRIM(I163))</x:f>
-        <x:v>场景|room_kit|tower_descent|root_3d|俯视3d|blender_review</x:v>
-      </x:c>
-      <x:c r="S163" t="str">
+      <x:c r="N164" s="70" t="str">
+        <x:v>GLB / 5×5×0.30m / 共享Mesh / MultiMesh平铺</x:v>
+      </x:c>
+      <x:c r="O164" s="70" t="str">
+        <x:v>assets/art/environments/tower_descent_3d/components/env_tower_floor_tile_5m_top3d_v001.glb</x:v>
+      </x:c>
+      <x:c r="P164" s="70" t="str">
+        <x:v>Blender集合=10A_MOD_FLOOR_TILE_5M_U01; export_env_tower_5m_modules_v001.py; TowerFloorStage3D.gd; verify_tower_descent_flow.tscn</x:v>
+      </x:c>
+      <x:c r="Q164" s="70" t="str">
+        <x:v>塔楼;地砖;楼板;5米;模块化;平铺;四向接口</x:v>
+      </x:c>
+      <x:c r="R164" s="70" t="str">
+        <x:v>场景|room_kit|tower_descent|floor_tile_5m|俯视3d|blender_review</x:v>
+      </x:c>
+      <x:c r="S164" s="70" t="str">
+        <x:v>母版子集合</x:v>
+      </x:c>
+      <x:c r="T164" s="70" t="str">
+        <x:v>987b220bef57c4176590caf7568c909d90768450c00f7e4e27c4c61986e6ef2d</x:v>
+      </x:c>
+      <x:c r="U164" s="70" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V164" s="71" t="n">
+        <x:v>46233</x:v>
+      </x:c>
+      <x:c r="W164" s="70" t="str">
+        <x:v>程序生成Blender源集合</x:v>
+      </x:c>
+      <x:c r="X164" s="70" t="str">
+        <x:v>PH44：整层由67×67调整为50×50个5m模块，物理尺寸250×250m、满铺2500块；地板仍由模块化MultiMesh渲染并保留独立StaticBody承重。四向楼梯洞口改用对齐5m世界矩形换算网格，避免尺寸与位移单位错位。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="165" ht="132" customHeight="1">
+      <x:c r="A165" s="70" t="str">
+        <x:v>ENV-TOWER-WALL-SOLID-5M</x:v>
+      </x:c>
+      <x:c r="B165" s="70" t="str">
+        <x:v>塔楼5米满高实墙模块</x:v>
+      </x:c>
+      <x:c r="C165" s="70" t="str">
+        <x:v>场景</x:v>
+      </x:c>
+      <x:c r="D165" s="70" t="str">
+        <x:v>room_kit</x:v>
+      </x:c>
+      <x:c r="E165" s="70" t="str">
+        <x:v>tower_descent</x:v>
+      </x:c>
+      <x:c r="F165" s="70" t="str">
+        <x:v>wall_solid_5m</x:v>
+      </x:c>
+      <x:c r="G165" s="70" t="str">
+        <x:v>ENV-TOWER-DESCENT-KIT-3D</x:v>
+      </x:c>
+      <x:c r="H165" s="70" t="str">
+        <x:v>俯视3D</x:v>
+      </x:c>
+      <x:c r="I165" s="70" t="str">
+        <x:v>godot_runtime</x:v>
+      </x:c>
+      <x:c r="J165" s="70" t="str">
+        <x:v>整层外墙/65m核心/探索房内墙/5m正交走廊</x:v>
+      </x:c>
+      <x:c r="K165" s="70" t="str">
+        <x:v>原型已接入</x:v>
+      </x:c>
+      <x:c r="L165" s="70" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="M165" s="70" t="str">
+        <x:v>v001</x:v>
+      </x:c>
+      <x:c r="N165" s="70" t="str">
+        <x:v>GLB / 5×0.30×9m / 共享Mesh / 可旋转</x:v>
+      </x:c>
+      <x:c r="O165" s="70" t="str">
+        <x:v>assets/art/environments/tower_descent_3d/components/env_tower_wall_solid_5m_top3d_v001.glb</x:v>
+      </x:c>
+      <x:c r="P165" s="70" t="str">
+        <x:v>Blender集合=10B_MOD_WALL_SOLID_5M_U01; export_env_tower_5m_modules_v001.py; DungeonRoom3D.gd; TowerFloorStage3D.gd</x:v>
+      </x:c>
+      <x:c r="Q165" s="70" t="str">
+        <x:v>塔楼;实墙;满高墙;5米;模块化;室内隔墙;核心外墙</x:v>
+      </x:c>
+      <x:c r="R165" s="70" t="str">
+        <x:v>场景|room_kit|tower_descent|wall_solid_5m|俯视3d|blender_review</x:v>
+      </x:c>
+      <x:c r="S165" s="70" t="str">
+        <x:v>母版子集合</x:v>
+      </x:c>
+      <x:c r="T165" s="70" t="str">
+        <x:v>5680bf2dedc964fcbfd5e5ee7d5ba86af5ba8a2c77c64a02151aee19a7f2cc33</x:v>
+      </x:c>
+      <x:c r="U165" s="70" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V165" s="71" t="n">
+        <x:v>46233</x:v>
+      </x:c>
+      <x:c r="W165" s="70" t="str">
+        <x:v>程序生成Blender源集合</x:v>
+      </x:c>
+      <x:c r="X165" s="70" t="str">
+        <x:v>PH44：继续复用同一5m实墙模块；45m战斗房每边按9个模块拼接。为控制250m楼层节点量，同方向连续实墙改为单个MultiMeshInstance3D批量渲染，碰撞按门洞两侧合并成长条StaticBody形状；视觉仍保持逐5m模块拼缝与命名语义。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="166" ht="132" customHeight="1">
+      <x:c r="A166" s="70" t="str">
+        <x:v>ENV-TOWER-WALL-PARAPET-5M</x:v>
+      </x:c>
+      <x:c r="B166" s="70" t="str">
+        <x:v>塔楼5米楼顶女儿墙模块</x:v>
+      </x:c>
+      <x:c r="C166" s="70" t="str">
+        <x:v>场景</x:v>
+      </x:c>
+      <x:c r="D166" s="70" t="str">
+        <x:v>room_kit</x:v>
+      </x:c>
+      <x:c r="E166" s="70" t="str">
+        <x:v>tower_descent</x:v>
+      </x:c>
+      <x:c r="F166" s="70" t="str">
+        <x:v>wall_parapet_5m</x:v>
+      </x:c>
+      <x:c r="G166" s="70" t="str">
+        <x:v>ENV-TOWER-DESCENT-KIT-3D</x:v>
+      </x:c>
+      <x:c r="H166" s="70" t="str">
+        <x:v>俯视3D</x:v>
+      </x:c>
+      <x:c r="I166" s="70" t="str">
+        <x:v>godot_runtime</x:v>
+      </x:c>
+      <x:c r="J166" s="70" t="str">
+        <x:v>335m楼顶四周边界/268段MultiMesh围栏</x:v>
+      </x:c>
+      <x:c r="K166" s="70" t="str">
+        <x:v>原型已接入</x:v>
+      </x:c>
+      <x:c r="L166" s="70" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="M166" s="70" t="str">
+        <x:v>v001</x:v>
+      </x:c>
+      <x:c r="N166" s="70" t="str">
+        <x:v>GLB / 5×0.30×1.50m / 共享Mesh</x:v>
+      </x:c>
+      <x:c r="O166" s="70" t="str">
+        <x:v>assets/art/environments/tower_descent_3d/components/env_tower_wall_parapet_5m_top3d_v001.glb</x:v>
+      </x:c>
+      <x:c r="P166" s="70" t="str">
+        <x:v>Blender集合=10C_MOD_WALL_PARAPET_5M_U01; export_env_tower_5m_modules_v001.py; TowerFloorStage3D.gd; verify_tower_descent_visual.tscn</x:v>
+      </x:c>
+      <x:c r="Q166" s="70" t="str">
+        <x:v>塔楼;女儿墙;护栏;5米;模块化;楼顶边界</x:v>
+      </x:c>
+      <x:c r="R166" s="70" t="str">
+        <x:v>场景|room_kit|tower_descent|wall_parapet_5m|俯视3d|blender_review</x:v>
+      </x:c>
+      <x:c r="S166" s="70" t="str">
+        <x:v>母版子集合</x:v>
+      </x:c>
+      <x:c r="T166" s="70" t="str">
+        <x:v>44fdb663487a9bf010d8fa249a2f9811843409c35d9f7ce8d09c48f7de7bf808</x:v>
+      </x:c>
+      <x:c r="U166" s="70" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V166" s="71" t="n">
+        <x:v>46233</x:v>
+      </x:c>
+      <x:c r="W166" s="70" t="str">
+        <x:v>程序生成Blender源集合</x:v>
+      </x:c>
+      <x:c r="X166" s="70" t="str">
+        <x:v>PH44：继续复用同一5m围栏模块，按50×50网格环绕250×250m楼顶与整层边界，不新增大块整体网格；普通楼顶由统一太阳照明，楼梯口局部阴影不再靠提高全局环境亮度解决。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="167" ht="132" customHeight="1">
+      <x:c r="A167" s="70" t="str">
+        <x:v>ENV-TOWER-WALL-DOOR-5M</x:v>
+      </x:c>
+      <x:c r="B167" s="70" t="str">
+        <x:v>塔楼5米带门墙模块</x:v>
+      </x:c>
+      <x:c r="C167" s="70" t="str">
+        <x:v>场景</x:v>
+      </x:c>
+      <x:c r="D167" s="70" t="str">
+        <x:v>room_kit</x:v>
+      </x:c>
+      <x:c r="E167" s="70" t="str">
+        <x:v>tower_descent</x:v>
+      </x:c>
+      <x:c r="F167" s="70" t="str">
+        <x:v>wall_door_5m</x:v>
+      </x:c>
+      <x:c r="G167" s="70" t="str">
+        <x:v>ENV-TOWER-DESCENT-KIT-3D</x:v>
+      </x:c>
+      <x:c r="H167" s="70" t="str">
+        <x:v>俯视3D</x:v>
+      </x:c>
+      <x:c r="I167" s="70" t="str">
+        <x:v>godot_runtime</x:v>
+      </x:c>
+      <x:c r="J167" s="70" t="str">
+        <x:v>塔楼房间门/走廊接口/楼梯门/命运触发</x:v>
+      </x:c>
+      <x:c r="K167" s="70" t="str">
+        <x:v>原型已接入</x:v>
+      </x:c>
+      <x:c r="L167" s="70" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="M167" s="70" t="str">
+        <x:v>v001</x:v>
+      </x:c>
+      <x:c r="N167" s="70" t="str">
+        <x:v>GLB / 5m墙位 / 4m净宽 / 4.5m净高 / 独立门扇</x:v>
+      </x:c>
+      <x:c r="O167" s="70" t="str">
+        <x:v>assets/art/environments/tower_descent_3d/components/env_tower_wall_door_5m_top3d_v001.glb</x:v>
+      </x:c>
+      <x:c r="P167" s="70" t="str">
+        <x:v>Blender集合=10D_MOD_WALL_DOOR_5M_U01; export_env_tower_5m_modules_v001.py; RoomDoor3D.gd; verify_tower_descent_flow.tscn</x:v>
+      </x:c>
+      <x:c r="Q167" s="70" t="str">
+        <x:v>塔楼;门;门洞;5米;模块化;肉鸽触发;独立门扇</x:v>
+      </x:c>
+      <x:c r="R167" s="70" t="str">
+        <x:v>场景|room_kit|tower_descent|wall_door_5m|俯视3d|blender_review</x:v>
+      </x:c>
+      <x:c r="S167" s="70" t="str">
+        <x:v>母版子集合</x:v>
+      </x:c>
+      <x:c r="T167" s="70" t="str">
+        <x:v>da5c2938eaca6360d945cdeb19d7af47c5ec64462c9065211191a9cf37deafe3</x:v>
+      </x:c>
+      <x:c r="U167" s="70" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V167" s="71" t="n">
+        <x:v>46233</x:v>
+      </x:c>
+      <x:c r="W167" s="70" t="str">
+        <x:v>程序生成Blender源集合</x:v>
+      </x:c>
+      <x:c r="X167" s="70" t="str">
+        <x:v>PH44：继续作为独立5m门墙语义模块；门洞不并入实墙MultiMesh，确保RoomDoor3D、命运卡、房间清理锁定与上下楼梯接口仍可逐门控制。上下层连接支持两端独立开口朝向。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="168" ht="132" customHeight="1">
+      <x:c r="A168" s="70" t="str">
+        <x:v>ENV-TOWER-STAIRWELL-GENERIC-9M</x:v>
+      </x:c>
+      <x:c r="B168" s="70" t="str">
+        <x:v>塔楼9米通用双跑楼梯间</x:v>
+      </x:c>
+      <x:c r="C168" s="70" t="str">
+        <x:v>场景</x:v>
+      </x:c>
+      <x:c r="D168" s="70" t="str">
+        <x:v>room_kit</x:v>
+      </x:c>
+      <x:c r="E168" s="70" t="str">
+        <x:v>tower_descent</x:v>
+      </x:c>
+      <x:c r="F168" s="70" t="str">
+        <x:v>stairwell_generic_9m</x:v>
+      </x:c>
+      <x:c r="G168" s="70" t="str">
+        <x:v>ENV-TOWER-DESCENT-KIT-3D</x:v>
+      </x:c>
+      <x:c r="H168" s="70" t="str">
+        <x:v>俯视3D</x:v>
+      </x:c>
+      <x:c r="I168" s="70" t="str">
+        <x:v>godot_runtime</x:v>
+      </x:c>
+      <x:c r="J168" s="70" t="str">
+        <x:v>99层以下通用楼梯/四向旋转/上下楼交通</x:v>
+      </x:c>
+      <x:c r="K168" s="70" t="str">
+        <x:v>原型已接入</x:v>
+      </x:c>
+      <x:c r="L168" s="70" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="M168" s="70" t="str">
+        <x:v>v001</x:v>
+      </x:c>
+      <x:c r="N168" s="70" t="str">
+        <x:v>GLB / 14.751×27.617×约18.41m包围 / 9m层差 / 48子对象</x:v>
+      </x:c>
+      <x:c r="O168" s="70" t="str">
+        <x:v>assets/art/environments/tower_descent_3d/components/env_tower_stairwell_generic_9m_top3d_v001.glb</x:v>
+      </x:c>
+      <x:c r="P168" s="70" t="str">
+        <x:v>Blender根=Stair_Generic_Rotatable_ROOT; env_tower_descent_kit_top3d_v006.blend; export_env_tower_stairwells_v001.py; TowerDescent3D.gd; verify_tower_descent_flow.tscn</x:v>
+      </x:c>
+      <x:c r="Q168" s="70" t="str">
+        <x:v>塔楼;通用楼梯;双跑楼梯;折角平台;9米层高;四向旋转;Blender直出</x:v>
+      </x:c>
+      <x:c r="R168" s="70" t="str">
+        <x:f>LOWER(TRIM(C168)&amp;"|"&amp;TRIM(D168)&amp;"|"&amp;TRIM(E168)&amp;"|"&amp;TRIM(F168)&amp;"|"&amp;TRIM(H168)&amp;"|"&amp;TRIM(I168))</x:f>
+        <x:v>场景|room_kit|tower_descent|stairwell_generic_9m|俯视3d|godot_runtime</x:v>
+      </x:c>
+      <x:c r="S168" s="70" t="str">
+        <x:f>IF(COUNTIF($R:$R,R168)&gt;1,"重复","唯一")</x:f>
         <x:v>唯一</x:v>
       </x:c>
-      <x:c r="T163" t="str">
-        <x:v>654d76f4f80ae41f183edf50e606ac4891b7cfe2cb76d01453fe07f25a810f1b</x:v>
-      </x:c>
-      <x:c r="U163" t="str">
+      <x:c r="T168" s="70" t="str">
+        <x:v>b0416e02b70673bb4cc38a58436210ff04343f6d68b4f5b80f8e1a0c5daaf844</x:v>
+      </x:c>
+      <x:c r="U168" s="70" t="str">
         <x:v>Codex</x:v>
       </x:c>
-      <x:c r="V163" t="n">
-        <x:v>46232</x:v>
-      </x:c>
-      <x:c r="W163" t="str">
-        <x:v>原创Blender程序建模</x:v>
-      </x:c>
-      <x:c r="X163" t="str">
-        <x:v>PH35评审母版：楼顶111.803×111.803m（12,500㎡）；设施/战斗层67.082×67.082m（4,500㎡）；层高9m。组件为6×6m门口走道、15×6m/下降4.5m固定斜坡、6×14m折角走道和27×14×9m双跑总成。已完成Blender尺寸/命名/接口QA与三张评审图；确认前不导出GLB、不修改Godot运行时。</x:v>
+      <x:c r="V168" s="71" t="n">
+        <x:v>46233</x:v>
+      </x:c>
+      <x:c r="W168" s="70" t="str">
+        <x:v>用户手工Blender模型</x:v>
+      </x:c>
+      <x:c r="X168" s="70" t="str">
+        <x:v>PH44：继续直接复用用户v006通用9m楼梯视觉与六块Walkable同形常驻碰撞；按5m世界矩形对齐250m整层中的四向楼梯洞口，可旋转通用。上下端门侧分别记录，避免楼梯开口朝向改变后沿用同一侧导致错位。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="169" ht="132" customHeight="1">
+      <x:c r="A169" s="70" t="str">
+        <x:v>ENV-TOWER-STAIRWELL-ROOFTOP-9M</x:v>
+      </x:c>
+      <x:c r="B169" s="70" t="str">
+        <x:v>塔楼楼顶特殊双跑楼梯间</x:v>
+      </x:c>
+      <x:c r="C169" s="70" t="str">
+        <x:v>场景</x:v>
+      </x:c>
+      <x:c r="D169" s="70" t="str">
+        <x:v>room_kit</x:v>
+      </x:c>
+      <x:c r="E169" s="70" t="str">
+        <x:v>tower_descent</x:v>
+      </x:c>
+      <x:c r="F169" s="70" t="str">
+        <x:v>stairwell_rooftop_9m</x:v>
+      </x:c>
+      <x:c r="G169" s="70" t="str">
+        <x:v>ENV-TOWER-DESCENT-KIT-3D</x:v>
+      </x:c>
+      <x:c r="H169" s="70" t="str">
+        <x:v>俯视3D</x:v>
+      </x:c>
+      <x:c r="I169" s="70" t="str">
+        <x:v>godot_runtime</x:v>
+      </x:c>
+      <x:c r="J169" s="70" t="str">
+        <x:v>楼顶至99层特殊交通/保留手调墙高</x:v>
+      </x:c>
+      <x:c r="K169" s="70" t="str">
+        <x:v>原型已接入</x:v>
+      </x:c>
+      <x:c r="L169" s="70" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="M169" s="70" t="str">
+        <x:v>v001</x:v>
+      </x:c>
+      <x:c r="N169" s="70" t="str">
+        <x:v>GLB / 14.751×27.617×约15.36m包围 / 9m层差 / 47子对象</x:v>
+      </x:c>
+      <x:c r="O169" s="70" t="str">
+        <x:v>assets/art/environments/tower_descent_3d/components/env_tower_stairwell_rooftop_9m_top3d_v001.glb</x:v>
+      </x:c>
+      <x:c r="P169" s="70" t="str">
+        <x:v>Blender根=Stair_Special_Rooftop_ROOT; env_tower_descent_kit_top3d_v006.blend; export_env_tower_stairwells_v001.py; TowerDescent3D.gd; verify_tower_descent_flow.tscn</x:v>
+      </x:c>
+      <x:c r="Q169" s="70" t="str">
+        <x:v>塔楼;楼顶楼梯;特殊楼梯;双跑楼梯;特殊墙高;9米层高;Blender直出</x:v>
+      </x:c>
+      <x:c r="R169" s="70" t="str">
+        <x:f>LOWER(TRIM(C169)&amp;"|"&amp;TRIM(D169)&amp;"|"&amp;TRIM(E169)&amp;"|"&amp;TRIM(F169)&amp;"|"&amp;TRIM(H169)&amp;"|"&amp;TRIM(I169))</x:f>
+        <x:v>场景|room_kit|tower_descent|stairwell_rooftop_9m|俯视3d|godot_runtime</x:v>
+      </x:c>
+      <x:c r="S169" s="70" t="str">
+        <x:f>IF(COUNTIF($R:$R,R169)&gt;1,"重复","唯一")</x:f>
+        <x:v>唯一</x:v>
+      </x:c>
+      <x:c r="T169" s="70" t="str">
+        <x:v>88198a579cc846974f17f5203b46b568b7ab2421fd7bb63c0b7868ddd05684a2</x:v>
+      </x:c>
+      <x:c r="U169" s="70" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="V169" s="71" t="n">
+        <x:v>46233</x:v>
+      </x:c>
+      <x:c r="W169" s="70" t="str">
+        <x:v>用户手工Blender模型</x:v>
+      </x:c>
+      <x:c r="X169" s="70" t="str">
+        <x:v>PH44：继续复用用户v006楼顶特殊楼梯、加高墙体及常驻Walkable/EnclosureWall碰撞。楼顶纯黑问题确认为固定斜俯视镜头被门墙整段遮挡；现仅剖切遮挡角色的墙体渲染，并联动同方向5m墙段，物理碰撞、门和楼梯围护保持有效；天空反弹光降至1.25，仅补兼容渲染器缺少实时天空GI。</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -12582,7 +13053,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1a1b9535d3ec4a02"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6ea5914e47234c5d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13721,373 +14192,373 @@
         <x:v>默认visible=false；不计入四主模块</x:v>
       </x:c>
     </x:row>
-    <x:row r="31" ht="62" customHeight="1">
-      <x:c r="A31" s="63" t="str">
+    <x:row r="31" ht="104" customHeight="1">
+      <x:c r="A31" s="70" t="str">
         <x:v>player_capsule01_bunny01_3d</x:v>
       </x:c>
-      <x:c r="B31" s="63" t="str">
+      <x:c r="B31" s="70" t="str">
         <x:v>root</x:v>
       </x:c>
-      <x:c r="C31" s="63" t="str">
+      <x:c r="C31" s="70" t="str">
         <x:v>Avatar3D/VisualRoot/BunnyRig</x:v>
       </x:c>
-      <x:c r="D31" s="63" t="str">
+      <x:c r="D31" s="70" t="str">
         <x:v>player_root</x:v>
       </x:c>
-      <x:c r="E31" s="63" t="str">
-        <x:v>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/chr_player_capsule01_bunny01_root_top3d_v004.tscn</x:v>
-      </x:c>
-      <x:c r="F31" s="63" t="str">
-        <x:v>Node3D刚性骨架</x:v>
-      </x:c>
-      <x:c r="G31" s="63" t="str">
+      <x:c r="E31" s="70" t="str">
+        <x:v>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/chr_player_capsule01_bunny01_root_top3d_v006.tscn</x:v>
+      </x:c>
+      <x:c r="F31" s="70" t="str">
+        <x:v>Node3D刚性骨架 / 完整视觉1.500m</x:v>
+      </x:c>
+      <x:c r="G31" s="70" t="str">
         <x:v>(0,0,0)</x:v>
       </x:c>
-      <x:c r="H31" s="63" t="str">
+      <x:c r="H31" s="70" t="str">
         <x:v>整体随准星绕Y轴</x:v>
       </x:c>
-      <x:c r="I31" s="63" t="n">
+      <x:c r="I31" s="70" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J31" s="63" t="str">
-        <x:v>六态整体 + 动作覆盖</x:v>
-      </x:c>
-      <x:c r="K31" s="63" t="str">
+      <x:c r="J31" s="70" t="str">
+        <x:v>八态整体 + falling收束/landing压缩回弹 + 动作覆盖</x:v>
+      </x:c>
+      <x:c r="K31" s="70" t="str">
         <x:v>Godot骨架根</x:v>
       </x:c>
-      <x:c r="L31" s="63" t="str">
+      <x:c r="L31" s="70" t="str">
         <x:v>是</x:v>
       </x:c>
-      <x:c r="M31" s="63" t="str">
-        <x:v>v004：模型为 pivot-local；导出器断言 Blender +X → Godot -Z；装配坐标由 Godot 关节节点提供；视觉层级 CollisionShape3D/CollisionObject3D 数量均为 0。玩法碰撞仅使用 Player3D/VirtualCollisionBox（0.86×1.80×0.72m），不包含耳朵。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="32" ht="54" customHeight="1">
-      <x:c r="A32" s="63" t="str">
+      <x:c r="M31" s="70" t="str">
+        <x:v>PH43：v006真实1.5m分体网格与AssetID不变；玩法碰撞位于Player3D/VirtualCollisionCapsule（height=1.5m、radius=0.34m）。falling/landing复用既有Body/Head/Hands/Feet/EarSocket关节。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" ht="104" customHeight="1">
+      <x:c r="A32" s="70" t="str">
         <x:v>player_capsule01_bunny01_3d</x:v>
       </x:c>
-      <x:c r="B32" s="63" t="str">
+      <x:c r="B32" s="70" t="str">
         <x:v>body</x:v>
       </x:c>
-      <x:c r="C32" s="63" t="str">
+      <x:c r="C32" s="70" t="str">
         <x:v>VisualRoot/BunnyRig/BodyJoint/Model</x:v>
       </x:c>
-      <x:c r="D32" s="63" t="str">
+      <x:c r="D32" s="70" t="str">
         <x:v>BunnyRig</x:v>
       </x:c>
-      <x:c r="E32" s="63" t="str">
-        <x:v>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_player_capsule01_bunny01_body_top3d_v004.glb</x:v>
-      </x:c>
-      <x:c r="F32" s="63" t="str">
-        <x:v>pivot-local GLB</x:v>
-      </x:c>
-      <x:c r="G32" s="63" t="str">
-        <x:v>(-0.00005,0.255786,-0.001047)</x:v>
-      </x:c>
-      <x:c r="H32" s="63" t="str">
+      <x:c r="E32" s="70" t="str">
+        <x:v>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_player_capsule01_bunny01_body_top3d_v006.glb</x:v>
+      </x:c>
+      <x:c r="F32" s="70" t="str">
+        <x:v>pivot-local GLB / 1.5m比例</x:v>
+      </x:c>
+      <x:c r="G32" s="70" t="str">
+        <x:v>(-0.000030,0.155022,-0.000635)</x:v>
+      </x:c>
+      <x:c r="H32" s="70" t="str">
         <x:v>BodyJoint</x:v>
       </x:c>
-      <x:c r="I32" s="63" t="n">
+      <x:c r="I32" s="70" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J32" s="63" t="str">
+      <x:c r="J32" s="70" t="str">
         <x:v>呼吸/移动挤压/突进翻滚/受击</x:v>
       </x:c>
-      <x:c r="K32" s="63" t="str">
+      <x:c r="K32" s="70" t="str">
         <x:v>身体组件</x:v>
       </x:c>
-      <x:c r="L32" s="63" t="str">
+      <x:c r="L32" s="70" t="str">
         <x:v>是</x:v>
       </x:c>
-      <x:c r="M32" s="63" t="str">
-        <x:v>Blender 原点：身体底部中心</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="33" ht="54" customHeight="1">
-      <x:c r="A33" s="63" t="str">
+      <x:c r="M32" s="70" t="str">
+        <x:v>Blender原点：身体底部中心；v006真实1.5m几何。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" ht="104" customHeight="1">
+      <x:c r="A33" s="70" t="str">
         <x:v>player_capsule01_bunny01_3d</x:v>
       </x:c>
-      <x:c r="B33" s="63" t="str">
+      <x:c r="B33" s="70" t="str">
         <x:v>head</x:v>
       </x:c>
-      <x:c r="C33" s="63" t="str">
+      <x:c r="C33" s="70" t="str">
         <x:v>VisualRoot/BunnyRig/HeadJoint/Model</x:v>
       </x:c>
-      <x:c r="D33" s="63" t="str">
+      <x:c r="D33" s="70" t="str">
         <x:v>BunnyRig</x:v>
       </x:c>
-      <x:c r="E33" s="63" t="str">
-        <x:v>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_player_capsule01_bunny01_head_top3d_v004.glb</x:v>
-      </x:c>
-      <x:c r="F33" s="63" t="str">
-        <x:v>pivot-local GLB</x:v>
-      </x:c>
-      <x:c r="G33" s="63" t="str">
-        <x:v>(-0.000046,0.787232,0.043611)</x:v>
-      </x:c>
-      <x:c r="H33" s="63" t="str">
+      <x:c r="E33" s="70" t="str">
+        <x:v>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_player_capsule01_bunny01_head_top3d_v006.glb</x:v>
+      </x:c>
+      <x:c r="F33" s="70" t="str">
+        <x:v>pivot-local GLB / 1.5m比例</x:v>
+      </x:c>
+      <x:c r="G33" s="70" t="str">
+        <x:v>(-0.000028,0.477110,0.026431)</x:v>
+      </x:c>
+      <x:c r="H33" s="70" t="str">
         <x:v>HeadJoint</x:v>
       </x:c>
-      <x:c r="I33" s="63" t="n">
+      <x:c r="I33" s="70" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="J33" s="63" t="str">
+      <x:c r="J33" s="70" t="str">
         <x:v>移动反相滞后/后坐/受击甩头</x:v>
       </x:c>
-      <x:c r="K33" s="63" t="str">
+      <x:c r="K33" s="70" t="str">
         <x:v>头部组件</x:v>
       </x:c>
-      <x:c r="L33" s="63" t="str">
+      <x:c r="L33" s="70" t="str">
         <x:v>是</x:v>
       </x:c>
-      <x:c r="M33" s="63" t="str">
-        <x:v>Blender 原点：头部下沿中心</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="34" ht="54" customHeight="1">
-      <x:c r="A34" s="63" t="str">
+      <x:c r="M33" s="70" t="str">
+        <x:v>Blender原点：头部下沿中心；不含耳头顶1.103390m。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" ht="104" customHeight="1">
+      <x:c r="A34" s="70" t="str">
         <x:v>player_capsule01_bunny01_3d</x:v>
       </x:c>
-      <x:c r="B34" s="63" t="str">
+      <x:c r="B34" s="70" t="str">
         <x:v>ear_l</x:v>
       </x:c>
-      <x:c r="C34" s="63" t="str">
+      <x:c r="C34" s="70" t="str">
         <x:v>VisualRoot/BunnyRig/HeadJoint/Ears/EarSocketL/EarAccessory</x:v>
       </x:c>
-      <x:c r="D34" s="63" t="str">
+      <x:c r="D34" s="70" t="str">
         <x:v>head</x:v>
       </x:c>
-      <x:c r="E34" s="63" t="str">
-        <x:v>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_player_capsule01_bunny01_ear_top3d_v004.glb</x:v>
-      </x:c>
-      <x:c r="F34" s="63" t="str">
-        <x:v>pivot-local GLB × -X</x:v>
-      </x:c>
-      <x:c r="G34" s="63" t="str">
-        <x:v>Head local (-0.404343,0.824427,-0.002757)</x:v>
-      </x:c>
-      <x:c r="H34" s="63" t="str">
+      <x:c r="E34" s="70" t="str">
+        <x:v>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_player_capsule01_bunny01_ear_top3d_v006.glb</x:v>
+      </x:c>
+      <x:c r="F34" s="70" t="str">
+        <x:v>pivot-local GLB × -X / 1.5m比例</x:v>
+      </x:c>
+      <x:c r="G34" s="70" t="str">
+        <x:v>Head local (-0.245056,0.499653,-0.001671)</x:v>
+      </x:c>
+      <x:c r="H34" s="70" t="str">
         <x:v>继承HeadJoint</x:v>
       </x:c>
-      <x:c r="I34" s="63" t="n">
+      <x:c r="I34" s="70" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="J34" s="63" t="str">
+      <x:c r="J34" s="70" t="str">
         <x:v>移动跟随/冲刺后压/受击收耳</x:v>
       </x:c>
-      <x:c r="K34" s="63" t="str">
+      <x:c r="K34" s="70" t="str">
         <x:v>头部配件</x:v>
       </x:c>
-      <x:c r="L34" s="63" t="str">
+      <x:c r="L34" s="70" t="str">
         <x:v>是</x:v>
       </x:c>
-      <x:c r="M34" s="63" t="str">
-        <x:v>复用语义右耳资产并在左挂点镜像；原点位于耳根</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="35" ht="54" customHeight="1">
-      <x:c r="A35" s="63" t="str">
+      <x:c r="M34" s="70" t="str">
+        <x:v>复用语义右耳并在左挂点镜像；完整视觉顶部1.500m。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" ht="104" customHeight="1">
+      <x:c r="A35" s="70" t="str">
         <x:v>player_capsule01_bunny01_3d</x:v>
       </x:c>
-      <x:c r="B35" s="63" t="str">
+      <x:c r="B35" s="70" t="str">
         <x:v>ear_r</x:v>
       </x:c>
-      <x:c r="C35" s="63" t="str">
+      <x:c r="C35" s="70" t="str">
         <x:v>VisualRoot/BunnyRig/HeadJoint/Ears/EarSocketR/EarAccessory</x:v>
       </x:c>
-      <x:c r="D35" s="63" t="str">
+      <x:c r="D35" s="70" t="str">
         <x:v>head</x:v>
       </x:c>
-      <x:c r="E35" s="63" t="str">
-        <x:v>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_player_capsule01_bunny01_ear_top3d_v004.glb</x:v>
-      </x:c>
-      <x:c r="F35" s="63" t="str">
-        <x:v>pivot-local GLB</x:v>
-      </x:c>
-      <x:c r="G35" s="63" t="str">
-        <x:v>Head local (0.404435,0.824427,-0.002757)</x:v>
-      </x:c>
-      <x:c r="H35" s="63" t="str">
+      <x:c r="E35" s="70" t="str">
+        <x:v>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_player_capsule01_bunny01_ear_top3d_v006.glb</x:v>
+      </x:c>
+      <x:c r="F35" s="70" t="str">
+        <x:v>pivot-local GLB / 1.5m比例</x:v>
+      </x:c>
+      <x:c r="G35" s="70" t="str">
+        <x:v>Head local (0.245112,0.499653,-0.001671)</x:v>
+      </x:c>
+      <x:c r="H35" s="70" t="str">
         <x:v>继承HeadJoint</x:v>
       </x:c>
-      <x:c r="I35" s="63" t="n">
+      <x:c r="I35" s="70" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="J35" s="63" t="str">
+      <x:c r="J35" s="70" t="str">
         <x:v>移动跟随/冲刺后压/受击收耳</x:v>
       </x:c>
-      <x:c r="K35" s="63" t="str">
+      <x:c r="K35" s="70" t="str">
         <x:v>头部配件</x:v>
       </x:c>
-      <x:c r="L35" s="63" t="str">
+      <x:c r="L35" s="70" t="str">
         <x:v>是</x:v>
       </x:c>
-      <x:c r="M35" s="63" t="str">
-        <x:v>语义右耳标准实例；原点位于耳根</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="36" ht="62" customHeight="1">
-      <x:c r="A36" s="63" t="str">
+      <x:c r="M35" s="70" t="str">
+        <x:v>语义右耳标准实例；完整视觉顶部1.500m。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" ht="104" customHeight="1">
+      <x:c r="A36" s="70" t="str">
         <x:v>player_capsule01_bunny01_3d</x:v>
       </x:c>
-      <x:c r="B36" s="63" t="str">
+      <x:c r="B36" s="70" t="str">
         <x:v>hand_l</x:v>
       </x:c>
-      <x:c r="C36" s="63" t="str">
+      <x:c r="C36" s="70" t="str">
         <x:v>VisualRoot/BunnyRig/HandRoot/HandJointL/Model</x:v>
       </x:c>
-      <x:c r="D36" s="63" t="str">
+      <x:c r="D36" s="70" t="str">
         <x:v>BunnyRig</x:v>
       </x:c>
-      <x:c r="E36" s="63" t="str">
-        <x:v>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_player_capsule01_bunny01_hand_l_top3d_v004.glb</x:v>
-      </x:c>
-      <x:c r="F36" s="63" t="str">
-        <x:v>pivot-local GLB</x:v>
-      </x:c>
-      <x:c r="G36" s="63" t="str">
-        <x:v>Authored (-0.471625,0.530925,-0.023818); longgun support (0.20,0.52,-0.64)</x:v>
-      </x:c>
-      <x:c r="H36" s="63" t="str">
+      <x:c r="E36" s="70" t="str">
+        <x:v>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_player_capsule01_bunny01_hand_l_top3d_v006.glb</x:v>
+      </x:c>
+      <x:c r="F36" s="70" t="str">
+        <x:v>pivot-local GLB / 1.5m比例</x:v>
+      </x:c>
+      <x:c r="G36" s="70" t="str">
+        <x:v>Authored (-0.285833,0.321773,-0.014435); longgun support (0.121212,0.315152,-0.387879)</x:v>
+      </x:c>
+      <x:c r="H36" s="70" t="str">
         <x:v>HandRoot 独立左腕</x:v>
       </x:c>
-      <x:c r="I36" s="63" t="n">
+      <x:c r="I36" s="70" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="J36" s="63" t="str">
+      <x:c r="J36" s="70" t="str">
         <x:v>手枪自由摆臂；长枪托举；换弹服务；双手枪后坐</x:v>
       </x:c>
-      <x:c r="K36" s="63" t="str">
+      <x:c r="K36" s="70" t="str">
         <x:v>左手组件</x:v>
       </x:c>
-      <x:c r="L36" s="63" t="str">
+      <x:c r="L36" s="70" t="str">
         <x:v>是</x:v>
       </x:c>
-      <x:c r="M36" s="63" t="str">
-        <x:v>Blender 原点位于手腕圆环近端轴心，球体为远端手掌；手枪姿势不计入握持手，长枪左手跨中线托住护木下方并绕本地 Y 负向转入托举。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="37" ht="62" customHeight="1">
-      <x:c r="A37" s="63" t="str">
+      <x:c r="M36" s="70" t="str">
+        <x:v>手腕圆环近端轴心；网格、挂点与动作米制平移使用0.606060606比例。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" ht="104" customHeight="1">
+      <x:c r="A37" s="70" t="str">
         <x:v>player_capsule01_bunny01_3d</x:v>
       </x:c>
-      <x:c r="B37" s="63" t="str">
+      <x:c r="B37" s="70" t="str">
         <x:v>hand_r</x:v>
       </x:c>
-      <x:c r="C37" s="63" t="str">
+      <x:c r="C37" s="70" t="str">
         <x:v>VisualRoot/BunnyRig/HandRoot/HandJointR/Model</x:v>
       </x:c>
-      <x:c r="D37" s="63" t="str">
+      <x:c r="D37" s="70" t="str">
         <x:v>BunnyRig</x:v>
       </x:c>
-      <x:c r="E37" s="63" t="str">
-        <x:v>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_player_capsule01_bunny01_hand_r_top3d_v004.glb</x:v>
-      </x:c>
-      <x:c r="F37" s="63" t="str">
-        <x:v>pivot-local GLB</x:v>
-      </x:c>
-      <x:c r="G37" s="63" t="str">
-        <x:v>Authored (0.471625,0.530925,-0.023818); sidearm (0.08,0.56,-0.49)+socket X0.24; longgun (0.13,0.56,-0.49)</x:v>
-      </x:c>
-      <x:c r="H37" s="63" t="str">
+      <x:c r="E37" s="70" t="str">
+        <x:v>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_player_capsule01_bunny01_hand_r_top3d_v006.glb</x:v>
+      </x:c>
+      <x:c r="F37" s="70" t="str">
+        <x:v>pivot-local GLB / 1.5m比例</x:v>
+      </x:c>
+      <x:c r="G37" s="70" t="str">
+        <x:v>Authored (0.285833,0.321773,-0.014435); sidearm (0.048485,0.339394,-0.296970)+socket X0.145455; longgun (0.078788,0.339394,-0.296970)</x:v>
+      </x:c>
+      <x:c r="H37" s="70" t="str">
         <x:v>HandRoot 独立右腕 / WeaponSocket 跟随</x:v>
       </x:c>
-      <x:c r="I37" s="63" t="n">
+      <x:c r="I37" s="70" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="J37" s="63" t="str">
+      <x:c r="J37" s="70" t="str">
         <x:v>手枪/长枪主握把；独立跑步；武器差异射击后坐</x:v>
       </x:c>
-      <x:c r="K37" s="63" t="str">
+      <x:c r="K37" s="70" t="str">
         <x:v>右手组件</x:v>
       </x:c>
-      <x:c r="L37" s="63" t="str">
+      <x:c r="L37" s="70" t="str">
         <x:v>是</x:v>
       </x:c>
-      <x:c r="M37" s="63" t="str">
-        <x:v>Blender 原点位于手腕圆环近端轴心，球体为远端手掌；角色右侧单手枪绕本地 Y 正向对齐，长枪与左手托举共同锁定。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="38" ht="54" customHeight="1">
-      <x:c r="A38" s="63" t="str">
+      <x:c r="M37" s="70" t="str">
+        <x:v>右手主握把；持枪视觉与手/挂点使用同一0.606060606比例。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" ht="104" customHeight="1">
+      <x:c r="A38" s="70" t="str">
         <x:v>player_capsule01_bunny01_3d</x:v>
       </x:c>
-      <x:c r="B38" s="63" t="str">
+      <x:c r="B38" s="70" t="str">
         <x:v>foot_l</x:v>
       </x:c>
-      <x:c r="C38" s="63" t="str">
+      <x:c r="C38" s="70" t="str">
         <x:v>VisualRoot/BunnyRig/FeetRoot/FootJointL/Model</x:v>
       </x:c>
-      <x:c r="D38" s="63" t="str">
+      <x:c r="D38" s="70" t="str">
         <x:v>FeetRoot</x:v>
       </x:c>
-      <x:c r="E38" s="63" t="str">
-        <x:v>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_player_capsule01_bunny01_foot_l_top3d_v004.glb</x:v>
-      </x:c>
-      <x:c r="F38" s="63" t="str">
-        <x:v>pivot-local GLB</x:v>
-      </x:c>
-      <x:c r="G38" s="63" t="str">
-        <x:v>(-0.212854,0,-0.017964)</x:v>
-      </x:c>
-      <x:c r="H38" s="63" t="str">
+      <x:c r="E38" s="70" t="str">
+        <x:v>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_player_capsule01_bunny01_foot_l_top3d_v006.glb</x:v>
+      </x:c>
+      <x:c r="F38" s="70" t="str">
+        <x:v>pivot-local GLB / 1.5m比例</x:v>
+      </x:c>
+      <x:c r="G38" s="70" t="str">
+        <x:v>(-0.129002,0,-0.010887)</x:v>
+      </x:c>
+      <x:c r="H38" s="70" t="str">
         <x:v>独立FootJointL</x:v>
       </x:c>
-      <x:c r="I38" s="63" t="n">
+      <x:c r="I38" s="70" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J38" s="63" t="str">
-        <x:v>moving左脚/翻滚收腿/受击甩脚</x:v>
-      </x:c>
-      <x:c r="K38" s="63" t="str">
+      <x:c r="J38" s="70" t="str">
+        <x:v>moving左脚/翻滚收腿/受击甩脚/falling收腿/landing压缩</x:v>
+      </x:c>
+      <x:c r="K38" s="70" t="str">
         <x:v>左脚组件</x:v>
       </x:c>
-      <x:c r="L38" s="63" t="str">
+      <x:c r="L38" s="70" t="str">
         <x:v>是</x:v>
       </x:c>
-      <x:c r="M38" s="63" t="str">
-        <x:v>Blender 原点：脚底中心</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="39" ht="54" customHeight="1">
-      <x:c r="A39" s="63" t="str">
+      <x:c r="M38" s="70" t="str">
+        <x:v>Blender原点：脚底中心；静态最低点Y=0；PH43复用同一v006网格增加下落与落地程序动作。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" ht="104" customHeight="1">
+      <x:c r="A39" s="70" t="str">
         <x:v>player_capsule01_bunny01_3d</x:v>
       </x:c>
-      <x:c r="B39" s="63" t="str">
+      <x:c r="B39" s="70" t="str">
         <x:v>foot_r</x:v>
       </x:c>
-      <x:c r="C39" s="63" t="str">
+      <x:c r="C39" s="70" t="str">
         <x:v>VisualRoot/BunnyRig/FeetRoot/FootJointR/Model</x:v>
       </x:c>
-      <x:c r="D39" s="63" t="str">
+      <x:c r="D39" s="70" t="str">
         <x:v>FeetRoot</x:v>
       </x:c>
-      <x:c r="E39" s="63" t="str">
-        <x:v>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_player_capsule01_bunny01_foot_r_top3d_v004.glb</x:v>
-      </x:c>
-      <x:c r="F39" s="63" t="str">
-        <x:v>pivot-local GLB</x:v>
-      </x:c>
-      <x:c r="G39" s="63" t="str">
-        <x:v>(0.212854,0,-0.017964)</x:v>
-      </x:c>
-      <x:c r="H39" s="63" t="str">
+      <x:c r="E39" s="70" t="str">
+        <x:v>assets/art/characters/player/chr_player_capsule01_3d/variants/bunny01/components/chr_player_capsule01_bunny01_foot_r_top3d_v006.glb</x:v>
+      </x:c>
+      <x:c r="F39" s="70" t="str">
+        <x:v>pivot-local GLB / 1.5m比例</x:v>
+      </x:c>
+      <x:c r="G39" s="70" t="str">
+        <x:v>(0.129002,0,-0.010887)</x:v>
+      </x:c>
+      <x:c r="H39" s="70" t="str">
         <x:v>独立FootJointR</x:v>
       </x:c>
-      <x:c r="I39" s="63" t="n">
+      <x:c r="I39" s="70" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J39" s="63" t="str">
-        <x:v>moving右脚/翻滚收腿/受击甩脚</x:v>
-      </x:c>
-      <x:c r="K39" s="63" t="str">
+      <x:c r="J39" s="70" t="str">
+        <x:v>moving右脚/翻滚收腿/受击甩脚/falling收腿/landing压缩</x:v>
+      </x:c>
+      <x:c r="K39" s="70" t="str">
         <x:v>右脚组件</x:v>
       </x:c>
-      <x:c r="L39" s="63" t="str">
+      <x:c r="L39" s="70" t="str">
         <x:v>是</x:v>
       </x:c>
-      <x:c r="M39" s="63" t="str">
-        <x:v>Blender 原点：脚底中心</x:v>
+      <x:c r="M39" s="70" t="str">
+        <x:v>Blender原点：脚底中心；静态最低点Y=0；PH43复用同一v006网格增加下落与落地程序动作。</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -14152,21 +14623,35 @@
       <x:c r="K2" s="3"/>
       <x:c r="L2" s="3"/>
     </x:row>
-    <x:row r="3" ht="23" customHeight="1">
-      <x:c r="A3" s="6" t="str">
-        <x:v>2D/3D 共用六态 ID 与转换白名单；Low HP / Silenced / Invincible / Reloading / Firing / Charging / Knockback 为叠加层。兔子另有武器姿势状态机：unarmed、sidearm/longgun × hold/run/fire/reload/charge。武器与命中是唯一动作来源，新增动画前先查本表</x:v>
-      </x:c>
-      <x:c r="B3" s="6"/>
-      <x:c r="C3" s="6"/>
-      <x:c r="D3" s="6"/>
-      <x:c r="E3" s="6"/>
-      <x:c r="F3" s="6"/>
-      <x:c r="G3" s="6"/>
-      <x:c r="H3" s="6"/>
-      <x:c r="I3" s="6"/>
-      <x:c r="J3" s="6"/>
-      <x:c r="K3" s="6"/>
-      <x:c r="L3" s="6"/>
+    <x:row r="3" ht="74" customHeight="1">
+      <x:c r="A3" s="96" t="str">
+        <x:v>Player3D 八态状态机 × 组件表现（falling/landing为真实垂直物理顶层状态）</x:v>
+      </x:c>
+      <x:c r="B3" s="96"/>
+      <x:c r="C3" s="96"/>
+      <x:c r="D3" s="96"/>
+      <x:c r="E3" s="96"/>
+      <x:c r="F3" s="96"/>
+      <x:c r="G3" s="96"/>
+      <x:c r="H3" s="96"/>
+      <x:c r="I3" s="96"/>
+      <x:c r="J3" s="96"/>
+      <x:c r="K3" s="96"/>
+      <x:c r="L3" s="96"/>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="70"/>
+      <x:c r="B4" s="70"/>
+      <x:c r="C4" s="70"/>
+      <x:c r="D4" s="70"/>
+      <x:c r="E4" s="70"/>
+      <x:c r="F4" s="70"/>
+      <x:c r="G4" s="70"/>
+      <x:c r="H4" s="70"/>
+      <x:c r="I4" s="70"/>
+      <x:c r="J4" s="70"/>
+      <x:c r="K4" s="70"/>
+      <x:c r="L4" s="70"/>
     </x:row>
     <x:row r="5" ht="32" customHeight="1">
       <x:c r="A5" s="28" t="str">
@@ -14207,1064 +14692,1182 @@
       </x:c>
     </x:row>
     <x:row r="6" ht="58" customHeight="1">
-      <x:c r="A6" s="36" t="str">
+      <x:c r="A6" s="100" t="str">
         <x:v>顶层</x:v>
       </x:c>
-      <x:c r="B6" s="36" t="str">
+      <x:c r="B6" s="100" t="str">
         <x:v>idle</x:v>
       </x:c>
-      <x:c r="C6" s="36" t="str">
+      <x:c r="C6" s="100" t="str">
         <x:v>待命</x:v>
       </x:c>
-      <x:c r="D6" s="36" t="str">
-        <x:v>start/moving/hurt/locked</x:v>
-      </x:c>
-      <x:c r="E6" s="36" t="str">
-        <x:v>moving,dashing,hurt,locked,dead</x:v>
-      </x:c>
-      <x:c r="F6" s="36" t="str">
+      <x:c r="D6" s="100" t="str">
+        <x:v>start/moving/hurt/locked/landing</x:v>
+      </x:c>
+      <x:c r="E6" s="100" t="str">
+        <x:v>moving,dashing,hurt,locked,falling,dead</x:v>
+      </x:c>
+      <x:c r="F6" s="100" t="str">
         <x:v>约2.38s呼吸挤压；半速重心换脚；躯干轻微侧移</x:v>
       </x:c>
-      <x:c r="G6" s="36" t="str">
+      <x:c r="G6" s="100" t="str">
         <x:v>与身体反相缩放；反向滞后保持头重感</x:v>
       </x:c>
-      <x:c r="H6" s="36" t="str">
+      <x:c r="H6" s="100" t="str">
         <x:v>手枪自由左手轻摆；长枪左手保持托举</x:v>
       </x:c>
-      <x:c r="I6" s="36" t="str">
+      <x:c r="I6" s="100" t="str">
         <x:v>握持手与 WeaponSocket 同步稳定呼吸，不脱离握把</x:v>
       </x:c>
-      <x:c r="J6" s="36" t="str">
+      <x:c r="J6" s="100" t="str">
         <x:v>低频错相轻摆</x:v>
       </x:c>
-      <x:c r="K6" s="36" t="str">
+      <x:c r="K6" s="100" t="str">
         <x:v>HUD 待命；无新增VFX</x:v>
       </x:c>
-      <x:c r="L6" s="36" t="str">
-        <x:v>六态 StateMachine 的 idle 唯一驱动；idle_cycle 推进呼吸/换脚；双耳错相并偶发单耳轻弹；moving 本帧归零，停下后恢复</x:v>
+      <x:c r="L6" s="100" t="str">
+        <x:v>八态 StateMachine 的 idle 唯一驱动；idle_cycle 推进呼吸/换脚；双耳错相并偶发单耳轻弹；moving 本帧归零，停下后恢复</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" s="37" t="str">
+      <x:c r="A7" s="101" t="str">
         <x:v>顶层</x:v>
       </x:c>
-      <x:c r="B7" s="37" t="str">
+      <x:c r="B7" s="101" t="str">
         <x:v>moving</x:v>
       </x:c>
-      <x:c r="C7" s="37" t="str">
+      <x:c r="C7" s="101" t="str">
         <x:v>机动</x:v>
       </x:c>
-      <x:c r="D7" s="37" t="str">
-        <x:v>idle/dashing/hurt/locked</x:v>
-      </x:c>
-      <x:c r="E7" s="37" t="str">
-        <x:v>idle,dashing,hurt,locked,dead</x:v>
-      </x:c>
-      <x:c r="F7" s="37" t="str">
+      <x:c r="D7" s="101" t="str">
+        <x:v>idle/dashing/hurt/locked/landing</x:v>
+      </x:c>
+      <x:c r="E7" s="101" t="str">
+        <x:v>idle,dashing,hurt,locked,falling,dead</x:v>
+      </x:c>
+      <x:c r="F7" s="101" t="str">
         <x:v>位移驱动弹跳/压缩回弹</x:v>
       </x:c>
-      <x:c r="G7" s="37" t="str">
+      <x:c r="G7" s="101" t="str">
         <x:v>较小反相滞后</x:v>
       </x:c>
-      <x:c r="H7" s="37" t="str">
+      <x:c r="H7" s="101" t="str">
         <x:v>手枪自由左手大幅反摆；长枪左手锁定托举</x:v>
       </x:c>
-      <x:c r="I7" s="37" t="str">
+      <x:c r="I7" s="101" t="str">
         <x:v>手枪右手与右侧挂点紧凑起伏；长枪双手/挂点收胸跑</x:v>
       </x:c>
-      <x:c r="J7" s="37" t="str">
+      <x:c r="J7" s="101" t="str">
         <x:v>周期滞后</x:v>
       </x:c>
-      <x:c r="K7" s="37" t="str">
+      <x:c r="K7" s="101" t="str">
         <x:v>地面划痕</x:v>
       </x:c>
-      <x:c r="L7" s="37" t="str">
+      <x:c r="L7" s="101" t="str">
         <x:v>位移驱动独立循环；WeaponPoseFSM 进入 sidearm_run 或 longgun_run；双脚交替，单手/双手剪影分离</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="56" customHeight="1">
-      <x:c r="A8" s="37" t="str">
+      <x:c r="A8" s="101" t="str">
         <x:v>顶层</x:v>
       </x:c>
-      <x:c r="B8" s="37" t="str">
+      <x:c r="B8" s="101" t="str">
         <x:v>dashing</x:v>
       </x:c>
-      <x:c r="C8" s="37" t="str">
+      <x:c r="C8" s="101" t="str">
         <x:v>突进</x:v>
       </x:c>
-      <x:c r="D8" s="37" t="str">
+      <x:c r="D8" s="101" t="str">
         <x:v>idle/moving</x:v>
       </x:c>
-      <x:c r="E8" s="37" t="str">
-        <x:v>idle,moving,hurt,locked,dead</x:v>
-      </x:c>
-      <x:c r="F8" s="37" t="str">
+      <x:c r="E8" s="101" t="str">
+        <x:v>idle,moving,hurt,locked,falling,dead</x:v>
+      </x:c>
+      <x:c r="F8" s="101" t="str">
         <x:v>压缩成团并绕半高轴完整前滚</x:v>
       </x:c>
-      <x:c r="G8" s="37" t="str">
+      <x:c r="G8" s="101" t="str">
         <x:v>随整体轴心翻滚，耳朵大幅后压</x:v>
       </x:c>
-      <x:c r="H8" s="37" t="str">
+      <x:c r="H8" s="101" t="str">
         <x:v>按当前武器握持数收束；自由左手随整体抱团</x:v>
       </x:c>
-      <x:c r="I8" s="37" t="str">
+      <x:c r="I8" s="101" t="str">
         <x:v>右手握把与 WeaponSocket 同轴完整翻滚</x:v>
       </x:c>
-      <x:c r="J8" s="37" t="str">
+      <x:c r="J8" s="101" t="str">
         <x:v>随整体收束</x:v>
       </x:c>
-      <x:c r="K8" s="37" t="str">
+      <x:c r="K8" s="101" t="str">
         <x:v>青色尾迹</x:v>
       </x:c>
-      <x:c r="L8" s="37" t="str">
+      <x:c r="L8" s="101" t="str">
         <x:v>0.17s 内完成 360° 本地X前滚；用半高轴心补偿避免钻地；夸张压缩与抛物线位移</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="56" customHeight="1">
-      <x:c r="A9" s="37" t="str">
+      <x:c r="A9" s="101" t="str">
         <x:v>顶层</x:v>
       </x:c>
-      <x:c r="B9" s="37" t="str">
+      <x:c r="B9" s="101" t="str">
         <x:v>hurt</x:v>
       </x:c>
-      <x:c r="C9" s="37" t="str">
+      <x:c r="C9" s="101" t="str">
         <x:v>受创</x:v>
       </x:c>
-      <x:c r="D9" s="37" t="str">
+      <x:c r="D9" s="101" t="str">
         <x:v>任意存活态</x:v>
       </x:c>
-      <x:c r="E9" s="37" t="str">
-        <x:v>idle,moving,locked,dead</x:v>
-      </x:c>
-      <x:c r="F9" s="37" t="str">
+      <x:c r="E9" s="101" t="str">
+        <x:v>idle,moving,locked,falling,dead</x:v>
+      </x:c>
+      <x:c r="F9" s="101" t="str">
         <x:v>三段压扁/抬起/过冲回正</x:v>
       </x:c>
-      <x:c r="G9" s="37" t="str">
+      <x:c r="G9" s="101" t="str">
         <x:v>大幅后仰甩头 + 反向过冲</x:v>
       </x:c>
-      <x:c r="H9" s="37" t="str">
+      <x:c r="H9" s="101" t="str">
         <x:v>手枪左手自由外甩；长枪左手回护木</x:v>
       </x:c>
-      <x:c r="I9" s="37" t="str">
+      <x:c r="I9" s="101" t="str">
         <x:v>右手/WeaponSocket 同相后退，握把不脱离</x:v>
       </x:c>
-      <x:c r="J9" s="37" t="str">
+      <x:c r="J9" s="101" t="str">
         <x:v>冲击滞后</x:v>
       </x:c>
-      <x:c r="K9" s="37" t="str">
+      <x:c r="K9" s="101" t="str">
         <x:v>红闪/击退轨迹</x:v>
       </x:c>
-      <x:c r="L9" s="37" t="str">
+      <x:c r="L9" s="101" t="str">
         <x:v>真实命中方向 + 受击进度关键姿势；头、双脚、双耳使用独立夸张回弹</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" s="37" t="str">
+      <x:c r="A10" s="101" t="str">
         <x:v>顶层</x:v>
       </x:c>
-      <x:c r="B10" s="37" t="str">
+      <x:c r="B10" s="101" t="str">
         <x:v>locked</x:v>
       </x:c>
-      <x:c r="C10" s="37" t="str">
+      <x:c r="C10" s="101" t="str">
         <x:v>交互锁定</x:v>
       </x:c>
-      <x:c r="D10" s="37" t="str">
+      <x:c r="D10" s="101" t="str">
+        <x:v>任意存活态/landing</x:v>
+      </x:c>
+      <x:c r="E10" s="101" t="str">
+        <x:v>idle,moving,hurt,falling,dead</x:v>
+      </x:c>
+      <x:c r="F10" s="101" t="str">
+        <x:v>降亮稳定</x:v>
+      </x:c>
+      <x:c r="G10" s="101" t="str">
+        <x:v>稳定</x:v>
+      </x:c>
+      <x:c r="H10" s="101" t="str">
+        <x:v>稳定</x:v>
+      </x:c>
+      <x:c r="I10" s="101" t="str">
+        <x:v>保持握持</x:v>
+      </x:c>
+      <x:c r="J10" s="101" t="str">
+        <x:v>低摆</x:v>
+      </x:c>
+      <x:c r="K10" s="101" t="str">
+        <x:v>琥珀锁定环</x:v>
+      </x:c>
+      <x:c r="L10" s="101" t="str">
+        <x:v>降亮 + 锁定环；保持刚性层级</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="92" customHeight="1">
+      <x:c r="A11" s="101" t="str">
+        <x:v>顶层</x:v>
+      </x:c>
+      <x:c r="B11" s="101" t="str">
+        <x:v>falling</x:v>
+      </x:c>
+      <x:c r="C11" s="101" t="str">
+        <x:v>下落</x:v>
+      </x:c>
+      <x:c r="D11" s="101" t="str">
+        <x:v>idle/moving/dashing/hurt/locked</x:v>
+      </x:c>
+      <x:c r="E11" s="101" t="str">
+        <x:v>landing,hurt,dead</x:v>
+      </x:c>
+      <x:c r="F11" s="101" t="str">
+        <x:v>随下落速度轻微纵向拉长</x:v>
+      </x:c>
+      <x:c r="G11" s="101" t="str">
+        <x:v>滞后上扬，保持头重感</x:v>
+      </x:c>
+      <x:c r="H11" s="101" t="str">
+        <x:v>手枪自由手收束；长枪托举手不脱离</x:v>
+      </x:c>
+      <x:c r="I11" s="101" t="str">
+        <x:v>握持手与WeaponSocket保持同相</x:v>
+      </x:c>
+      <x:c r="J11" s="101" t="str">
+        <x:v>向上滞后</x:v>
+      </x:c>
+      <x:c r="K11" s="101" t="str">
+        <x:v>无新增VFX</x:v>
+      </x:c>
+      <x:c r="L11" s="101" t="str">
+        <x:v>真实重力+0.10s离地容错；双脚收起、双耳后压；楼梯接缝不误触发</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="92" customHeight="1">
+      <x:c r="A12" s="101" t="str">
+        <x:v>顶层</x:v>
+      </x:c>
+      <x:c r="B12" s="101" t="str">
+        <x:v>landing</x:v>
+      </x:c>
+      <x:c r="C12" s="101" t="str">
+        <x:v>落地</x:v>
+      </x:c>
+      <x:c r="D12" s="101" t="str">
+        <x:v>falling</x:v>
+      </x:c>
+      <x:c r="E12" s="101" t="str">
+        <x:v>idle,moving,locked,falling,hurt,dead</x:v>
+      </x:c>
+      <x:c r="F12" s="101" t="str">
+        <x:v>按冲击速度压缩并回弹</x:v>
+      </x:c>
+      <x:c r="G12" s="101" t="str">
+        <x:v>轻微下压后恢复</x:v>
+      </x:c>
+      <x:c r="H12" s="101" t="str">
+        <x:v>随整体吸收冲击</x:v>
+      </x:c>
+      <x:c r="I12" s="101" t="str">
+        <x:v>握持手与WeaponSocket同相稳定</x:v>
+      </x:c>
+      <x:c r="J12" s="101" t="str">
+        <x:v>短促回摆</x:v>
+      </x:c>
+      <x:c r="K12" s="101" t="str">
+        <x:v>落地停顿</x:v>
+      </x:c>
+      <x:c r="L12" s="101" t="str">
+        <x:v>冲击速度映射0.12—0.30s硬直；状态计时结束后恢复地面移动</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="101" t="str">
+        <x:v>顶层</x:v>
+      </x:c>
+      <x:c r="B13" s="101" t="str">
+        <x:v>dead</x:v>
+      </x:c>
+      <x:c r="C13" s="101" t="str">
+        <x:v>生命终止</x:v>
+      </x:c>
+      <x:c r="D13" s="101" t="str">
         <x:v>任意存活态</x:v>
       </x:c>
-      <x:c r="E10" s="37" t="str">
-        <x:v>idle,moving,hurt,dead</x:v>
-      </x:c>
-      <x:c r="F10" s="37" t="str">
-        <x:v>降亮稳定</x:v>
-      </x:c>
-      <x:c r="G10" s="37" t="str">
+      <x:c r="E13" s="101" t="str">
+        <x:v>无（终态）</x:v>
+      </x:c>
+      <x:c r="F13" s="101" t="str">
+        <x:v>倾倒熄灭</x:v>
+      </x:c>
+      <x:c r="G13" s="101" t="str">
+        <x:v>随整体倾倒</x:v>
+      </x:c>
+      <x:c r="H13" s="101" t="str">
+        <x:v>随整体倾倒</x:v>
+      </x:c>
+      <x:c r="I13" s="101" t="str">
+        <x:v>随整体倾倒</x:v>
+      </x:c>
+      <x:c r="J13" s="101" t="str">
+        <x:v>停止</x:v>
+      </x:c>
+      <x:c r="K13" s="101" t="str">
+        <x:v>HUD 终止</x:v>
+      </x:c>
+      <x:c r="L13" s="101" t="str">
+        <x:v>整体倾倒；耳朵与肢体跟随关节</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="101" t="str">
+        <x:v>叠加</x:v>
+      </x:c>
+      <x:c r="B14" s="101" t="str">
+        <x:v>low_health</x:v>
+      </x:c>
+      <x:c r="C14" s="101" t="str">
+        <x:v>低血</x:v>
+      </x:c>
+      <x:c r="D14" s="101" t="str">
+        <x:v>任意存活态</x:v>
+      </x:c>
+      <x:c r="E14" s="101" t="str">
+        <x:v>不改变顶层</x:v>
+      </x:c>
+      <x:c r="F14" s="101" t="str">
+        <x:v>不变</x:v>
+      </x:c>
+      <x:c r="G14" s="101" t="str">
+        <x:v>不变</x:v>
+      </x:c>
+      <x:c r="H14" s="101" t="str">
+        <x:v>保持当前动作</x:v>
+      </x:c>
+      <x:c r="I14" s="101" t="str">
+        <x:v>保持当前动作</x:v>
+      </x:c>
+      <x:c r="J14" s="101" t="str">
+        <x:v>不变</x:v>
+      </x:c>
+      <x:c r="K14" s="101" t="str">
+        <x:v>红色呼吸环</x:v>
+      </x:c>
+      <x:c r="L14" s="101" t="str">
+        <x:v>HP≤30%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="56" customHeight="1">
+      <x:c r="A15" s="70" t="str">
+        <x:v>叠加</x:v>
+      </x:c>
+      <x:c r="B15" s="70" t="str">
+        <x:v>silenced</x:v>
+      </x:c>
+      <x:c r="C15" s="70" t="str">
+        <x:v>沉默</x:v>
+      </x:c>
+      <x:c r="D15" s="70" t="str">
+        <x:v>任意存活态</x:v>
+      </x:c>
+      <x:c r="E15" s="70" t="str">
+        <x:v>不改变顶层</x:v>
+      </x:c>
+      <x:c r="F15" s="70" t="str">
+        <x:v>降饱和可选</x:v>
+      </x:c>
+      <x:c r="G15" s="70" t="str">
+        <x:v>传感器干扰</x:v>
+      </x:c>
+      <x:c r="H15" s="70" t="str">
+        <x:v>保持当前动作</x:v>
+      </x:c>
+      <x:c r="I15" s="70" t="str">
+        <x:v>保持当前动作</x:v>
+      </x:c>
+      <x:c r="J15" s="70" t="str">
+        <x:v>不变</x:v>
+      </x:c>
+      <x:c r="K15" s="70" t="str">
+        <x:v>紫色干扰环</x:v>
+      </x:c>
+      <x:c r="L15" s="70" t="str">
+        <x:v>计时标志</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="28" customHeight="1">
+      <x:c r="A16" s="97" t="str">
+        <x:v>叠加</x:v>
+      </x:c>
+      <x:c r="B16" s="97" t="str">
+        <x:v>invincible</x:v>
+      </x:c>
+      <x:c r="C16" s="97" t="str">
+        <x:v>无敌</x:v>
+      </x:c>
+      <x:c r="D16" s="97" t="str">
+        <x:v>dash/hurt</x:v>
+      </x:c>
+      <x:c r="E16" s="97" t="str">
+        <x:v>不改变顶层</x:v>
+      </x:c>
+      <x:c r="F16" s="97" t="str">
+        <x:v>闪烁</x:v>
+      </x:c>
+      <x:c r="G16" s="97" t="str">
+        <x:v>闪烁</x:v>
+      </x:c>
+      <x:c r="H16" s="97" t="str">
+        <x:v>保持当前动作</x:v>
+      </x:c>
+      <x:c r="I16" s="97" t="str">
+        <x:v>保持当前动作</x:v>
+      </x:c>
+      <x:c r="J16" s="97" t="str">
+        <x:v>闪烁</x:v>
+      </x:c>
+      <x:c r="K16" s="97" t="str">
+        <x:v>透明闪烁</x:v>
+      </x:c>
+      <x:c r="L16" s="97" t="str">
+        <x:v>InvincibleTimer 唯一解除</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="36" customHeight="1">
+      <x:c r="A17" s="70" t="str">
+        <x:v>叠加</x:v>
+      </x:c>
+      <x:c r="B17" s="70" t="str">
+        <x:v>reloading</x:v>
+      </x:c>
+      <x:c r="C17" s="70" t="str">
+        <x:v>换弹</x:v>
+      </x:c>
+      <x:c r="D17" s="70" t="str">
+        <x:v>任意持枪存活态</x:v>
+      </x:c>
+      <x:c r="E17" s="70" t="str">
+        <x:v>不改变顶层；完成/取消退出</x:v>
+      </x:c>
+      <x:c r="F17" s="70" t="str">
+        <x:v>保持当前顶层</x:v>
+      </x:c>
+      <x:c r="G17" s="70" t="str">
+        <x:v>保持当前顶层</x:v>
+      </x:c>
+      <x:c r="H17" s="70" t="str">
+        <x:v>手枪左手近身取弹但不计握持；长枪左手离开护木服务</x:v>
+      </x:c>
+      <x:c r="I17" s="70" t="str">
+        <x:v>右手持续握把并跟随 WeaponSocket 下压/回位</x:v>
+      </x:c>
+      <x:c r="J17" s="70" t="str">
+        <x:v>保持当前顶层</x:v>
+      </x:c>
+      <x:c r="K17" s="70" t="str">
+        <x:v>3D头顶billboard进度条；2D弹药栏</x:v>
+      </x:c>
+      <x:c r="L17" s="70" t="str">
+        <x:v>WeaponModel3D 唯一计时源；WeaponPoseFSM 进入 sidearm_reload/longgun_reload；右手保持握把，左手按武器类型服务</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="42" customHeight="1">
+      <x:c r="A18" s="70" t="str">
+        <x:v>Enemy3D 九态状态机 × 模块表现 × 模型轮廓碰撞</x:v>
+      </x:c>
+      <x:c r="B18" s="70"/>
+      <x:c r="C18" s="70"/>
+      <x:c r="D18" s="70"/>
+      <x:c r="E18" s="70"/>
+      <x:c r="F18" s="70"/>
+      <x:c r="G18" s="70"/>
+      <x:c r="H18" s="70"/>
+      <x:c r="I18" s="70"/>
+      <x:c r="J18" s="70"/>
+      <x:c r="K18" s="70"/>
+      <x:c r="L18" s="70"/>
+    </x:row>
+    <x:row r="19" ht="42" customHeight="1">
+      <x:c r="A19" s="70" t="str">
+        <x:v>层级</x:v>
+      </x:c>
+      <x:c r="B19" s="70" t="str">
+        <x:v>状态ID</x:v>
+      </x:c>
+      <x:c r="C19" s="70" t="str">
+        <x:v>中文名</x:v>
+      </x:c>
+      <x:c r="D19" s="70" t="str">
+        <x:v>允许来源</x:v>
+      </x:c>
+      <x:c r="E19" s="70" t="str">
+        <x:v>允许去向</x:v>
+      </x:c>
+      <x:c r="F19" s="70" t="str">
+        <x:v>Core</x:v>
+      </x:c>
+      <x:c r="G19" s="70" t="str">
+        <x:v>Shell</x:v>
+      </x:c>
+      <x:c r="H19" s="70" t="str">
+        <x:v>Appendages</x:v>
+      </x:c>
+      <x:c r="I19" s="70" t="str">
+        <x:v>StateVFX</x:v>
+      </x:c>
+      <x:c r="J19" s="70" t="str">
+        <x:v>行为职责</x:v>
+      </x:c>
+      <x:c r="K19" s="70" t="str">
+        <x:v>验收</x:v>
+      </x:c>
+      <x:c r="L19" s="70" t="str">
+        <x:v>首版实现</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="42" customHeight="1">
+      <x:c r="A20" s="70" t="str">
+        <x:v>顶层</x:v>
+      </x:c>
+      <x:c r="B20" s="70" t="str">
+        <x:v>idle</x:v>
+      </x:c>
+      <x:c r="C20" s="70" t="str">
+        <x:v>待机</x:v>
+      </x:c>
+      <x:c r="D20" s="70" t="str">
+        <x:v>start/patrol/stagger</x:v>
+      </x:c>
+      <x:c r="E20" s="70" t="str">
+        <x:v>patrol/alert/dead</x:v>
+      </x:c>
+      <x:c r="F20" s="70" t="str">
+        <x:v>低频脉冲</x:v>
+      </x:c>
+      <x:c r="G20" s="70" t="str">
+        <x:v>轻浮动</x:v>
+      </x:c>
+      <x:c r="H20" s="70" t="str">
+        <x:v>低速</x:v>
+      </x:c>
+      <x:c r="I20" s="70" t="str">
+        <x:v>关闭</x:v>
+      </x:c>
+      <x:c r="J20" s="70" t="str">
+        <x:v>等待目标</x:v>
+      </x:c>
+      <x:c r="K20" s="70" t="str">
+        <x:v>静态轮廓可读</x:v>
+      </x:c>
+      <x:c r="L20" s="70" t="str">
+        <x:v>模块变换</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="42" customHeight="1">
+      <x:c r="A21" s="70" t="str">
+        <x:v>顶层</x:v>
+      </x:c>
+      <x:c r="B21" s="70" t="str">
+        <x:v>patrol</x:v>
+      </x:c>
+      <x:c r="C21" s="70" t="str">
+        <x:v>巡逻</x:v>
+      </x:c>
+      <x:c r="D21" s="70" t="str">
+        <x:v>idle/search</x:v>
+      </x:c>
+      <x:c r="E21" s="70" t="str">
+        <x:v>idle/alert/stagger/dead</x:v>
+      </x:c>
+      <x:c r="F21" s="70" t="str">
+        <x:v>低频脉冲</x:v>
+      </x:c>
+      <x:c r="G21" s="70" t="str">
+        <x:v>朝巡逻点</x:v>
+      </x:c>
+      <x:c r="H21" s="70" t="str">
+        <x:v>慢速步态</x:v>
+      </x:c>
+      <x:c r="I21" s="70" t="str">
+        <x:v>关闭</x:v>
+      </x:c>
+      <x:c r="J21" s="70" t="str">
+        <x:v>出生点附近巡逻</x:v>
+      </x:c>
+      <x:c r="K21" s="70" t="str">
+        <x:v>无目标不原地僵住</x:v>
+      </x:c>
+      <x:c r="L21" s="70" t="str">
+        <x:v>CharacterBody3D</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" ht="42" customHeight="1">
+      <x:c r="A22" s="70" t="str">
+        <x:v>顶层</x:v>
+      </x:c>
+      <x:c r="B22" s="70" t="str">
+        <x:v>alert</x:v>
+      </x:c>
+      <x:c r="C22" s="70" t="str">
+        <x:v>警觉</x:v>
+      </x:c>
+      <x:c r="D22" s="70" t="str">
+        <x:v>idle/patrol/search</x:v>
+      </x:c>
+      <x:c r="E22" s="70" t="str">
+        <x:v>chase/stagger/dead</x:v>
+      </x:c>
+      <x:c r="F22" s="70" t="str">
+        <x:v>加速</x:v>
+      </x:c>
+      <x:c r="G22" s="70" t="str">
+        <x:v>抬升</x:v>
+      </x:c>
+      <x:c r="H22" s="70" t="str">
+        <x:v>展开</x:v>
+      </x:c>
+      <x:c r="I22" s="70" t="str">
+        <x:v>关闭</x:v>
+      </x:c>
+      <x:c r="J22" s="70" t="str">
+        <x:v>发现玩家</x:v>
+      </x:c>
+      <x:c r="K22" s="70" t="str">
+        <x:v>0.28s响应</x:v>
+      </x:c>
+      <x:c r="L22" s="70" t="str">
+        <x:v>模块变换</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" ht="42" customHeight="1">
+      <x:c r="A23" s="70" t="str">
+        <x:v>顶层</x:v>
+      </x:c>
+      <x:c r="B23" s="70" t="str">
+        <x:v>chase</x:v>
+      </x:c>
+      <x:c r="C23" s="70" t="str">
+        <x:v>追击</x:v>
+      </x:c>
+      <x:c r="D23" s="70" t="str">
+        <x:v>alert/attack/stagger</x:v>
+      </x:c>
+      <x:c r="E23" s="70" t="str">
+        <x:v>search/telegraph/stagger/dead</x:v>
+      </x:c>
+      <x:c r="F23" s="70" t="str">
         <x:v>稳定</x:v>
       </x:c>
-      <x:c r="H10" s="37" t="str">
+      <x:c r="G23" s="70" t="str">
+        <x:v>朝目标</x:v>
+      </x:c>
+      <x:c r="H23" s="70" t="str">
+        <x:v>步态</x:v>
+      </x:c>
+      <x:c r="I23" s="70" t="str">
+        <x:v>关闭</x:v>
+      </x:c>
+      <x:c r="J23" s="70" t="str">
+        <x:v>距离控制</x:v>
+      </x:c>
+      <x:c r="K23" s="70" t="str">
+        <x:v>七类速度差</x:v>
+      </x:c>
+      <x:c r="L23" s="70" t="str">
+        <x:v>CharacterBody3D</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" ht="42" customHeight="1">
+      <x:c r="A24" s="70" t="str">
+        <x:v>顶层</x:v>
+      </x:c>
+      <x:c r="B24" s="70" t="str">
+        <x:v>search</x:v>
+      </x:c>
+      <x:c r="C24" s="70" t="str">
+        <x:v>搜索</x:v>
+      </x:c>
+      <x:c r="D24" s="70" t="str">
+        <x:v>chase</x:v>
+      </x:c>
+      <x:c r="E24" s="70" t="str">
+        <x:v>patrol/alert/stagger/dead</x:v>
+      </x:c>
+      <x:c r="F24" s="70" t="str">
+        <x:v>渐缓</x:v>
+      </x:c>
+      <x:c r="G24" s="70" t="str">
+        <x:v>朝最后位置</x:v>
+      </x:c>
+      <x:c r="H24" s="70" t="str">
+        <x:v>搜索步态</x:v>
+      </x:c>
+      <x:c r="I24" s="70" t="str">
+        <x:v>搜索提示</x:v>
+      </x:c>
+      <x:c r="J24" s="70" t="str">
+        <x:v>失去视线后搜索</x:v>
+      </x:c>
+      <x:c r="K24" s="70" t="str">
+        <x:v>2.4s后回巡逻</x:v>
+      </x:c>
+      <x:c r="L24" s="70" t="str">
+        <x:v>射线+最后位置</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" s="70" t="str">
+        <x:v>顶层</x:v>
+      </x:c>
+      <x:c r="B25" s="70" t="str">
+        <x:v>telegraph</x:v>
+      </x:c>
+      <x:c r="C25" s="70" t="str">
+        <x:v>预警</x:v>
+      </x:c>
+      <x:c r="D25" s="70" t="str">
+        <x:v>chase</x:v>
+      </x:c>
+      <x:c r="E25" s="70" t="str">
+        <x:v>attack/stagger/dead</x:v>
+      </x:c>
+      <x:c r="F25" s="70" t="str">
+        <x:v>高频脉冲</x:v>
+      </x:c>
+      <x:c r="G25" s="70" t="str">
         <x:v>稳定</x:v>
       </x:c>
-      <x:c r="I10" s="37" t="str">
-        <x:v>保持握持</x:v>
-      </x:c>
-      <x:c r="J10" s="37" t="str">
-        <x:v>低摆</x:v>
-      </x:c>
-      <x:c r="K10" s="37" t="str">
-        <x:v>琥珀锁定环</x:v>
-      </x:c>
-      <x:c r="L10" s="37" t="str">
-        <x:v>降亮 + 锁定环；保持刚性层级</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11">
-      <x:c r="A11" s="37" t="str">
+      <x:c r="H25" s="70" t="str">
+        <x:v>蓄势</x:v>
+      </x:c>
+      <x:c r="I25" s="70" t="str">
+        <x:v>红色预警环</x:v>
+      </x:c>
+      <x:c r="J25" s="70" t="str">
+        <x:v>攻击前摇</x:v>
+      </x:c>
+      <x:c r="K25" s="70" t="str">
+        <x:v>不可省略</x:v>
+      </x:c>
+      <x:c r="L25" s="70" t="str">
+        <x:v>计时状态</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26" s="70" t="str">
         <x:v>顶层</x:v>
       </x:c>
-      <x:c r="B11" s="37" t="str">
+      <x:c r="B26" s="70" t="str">
+        <x:v>attack</x:v>
+      </x:c>
+      <x:c r="C26" s="70" t="str">
+        <x:v>攻击</x:v>
+      </x:c>
+      <x:c r="D26" s="70" t="str">
+        <x:v>telegraph</x:v>
+      </x:c>
+      <x:c r="E26" s="70" t="str">
+        <x:v>chase/stagger/dead</x:v>
+      </x:c>
+      <x:c r="F26" s="70" t="str">
+        <x:v>峰值</x:v>
+      </x:c>
+      <x:c r="G26" s="70" t="str">
+        <x:v>反冲</x:v>
+      </x:c>
+      <x:c r="H26" s="70" t="str">
+        <x:v>执行</x:v>
+      </x:c>
+      <x:c r="I26" s="70" t="str">
+        <x:v>按攻击类型</x:v>
+      </x:c>
+      <x:c r="J26" s="70" t="str">
+        <x:v>近战/远程/召唤/爆炸</x:v>
+      </x:c>
+      <x:c r="K26" s="70" t="str">
+        <x:v>七类差异</x:v>
+      </x:c>
+      <x:c r="L26" s="70" t="str">
+        <x:v>profile策略</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27">
+      <x:c r="A27" s="70" t="str">
+        <x:v>顶层</x:v>
+      </x:c>
+      <x:c r="B27" s="70" t="str">
+        <x:v>stagger</x:v>
+      </x:c>
+      <x:c r="C27" s="70" t="str">
+        <x:v>硬直</x:v>
+      </x:c>
+      <x:c r="D27" s="70" t="str">
+        <x:v>任意存活态</x:v>
+      </x:c>
+      <x:c r="E27" s="70" t="str">
+        <x:v>chase/dead</x:v>
+      </x:c>
+      <x:c r="F27" s="70" t="str">
+        <x:v>闪色</x:v>
+      </x:c>
+      <x:c r="G27" s="70" t="str">
+        <x:v>冲击</x:v>
+      </x:c>
+      <x:c r="H27" s="70" t="str">
+        <x:v>暂停</x:v>
+      </x:c>
+      <x:c r="I27" s="70" t="str">
+        <x:v>伤害反馈</x:v>
+      </x:c>
+      <x:c r="J27" s="70" t="str">
+        <x:v>受击窗口</x:v>
+      </x:c>
+      <x:c r="K27" s="70" t="str">
+        <x:v>方向可读</x:v>
+      </x:c>
+      <x:c r="L27" s="70" t="str">
+        <x:v>统一伤害入口</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" ht="38" customHeight="1">
+      <x:c r="A28" s="102" t="str">
+        <x:v>顶层</x:v>
+      </x:c>
+      <x:c r="B28" s="102" t="str">
         <x:v>dead</x:v>
       </x:c>
-      <x:c r="C11" s="37" t="str">
-        <x:v>生命终止</x:v>
-      </x:c>
-      <x:c r="D11" s="37" t="str">
+      <x:c r="C28" s="102" t="str">
+        <x:v>死亡</x:v>
+      </x:c>
+      <x:c r="D28" s="102" t="str">
         <x:v>任意存活态</x:v>
       </x:c>
-      <x:c r="E11" s="37" t="str">
+      <x:c r="E28" s="102" t="str">
         <x:v>无（终态）</x:v>
       </x:c>
-      <x:c r="F11" s="37" t="str">
-        <x:v>倾倒熄灭</x:v>
-      </x:c>
-      <x:c r="G11" s="37" t="str">
-        <x:v>随整体倾倒</x:v>
-      </x:c>
-      <x:c r="H11" s="37" t="str">
-        <x:v>随整体倾倒</x:v>
-      </x:c>
-      <x:c r="I11" s="37" t="str">
-        <x:v>随整体倾倒</x:v>
-      </x:c>
-      <x:c r="J11" s="37" t="str">
+      <x:c r="F28" s="102" t="str">
+        <x:v>熄灭</x:v>
+      </x:c>
+      <x:c r="G28" s="102" t="str">
+        <x:v>压扁</x:v>
+      </x:c>
+      <x:c r="H28" s="102" t="str">
         <x:v>停止</x:v>
       </x:c>
-      <x:c r="K11" s="37" t="str">
-        <x:v>HUD 终止</x:v>
-      </x:c>
-      <x:c r="L11" s="37" t="str">
-        <x:v>整体倾倒；耳朵与肢体跟随关节</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12">
-      <x:c r="A12" s="37" t="str">
+      <x:c r="I28" s="102" t="str">
+        <x:v>爆散/淡出</x:v>
+      </x:c>
+      <x:c r="J28" s="102" t="str">
+        <x:v>掉落与计数</x:v>
+      </x:c>
+      <x:c r="K28" s="102" t="str">
+        <x:v>不可回存活态</x:v>
+      </x:c>
+      <x:c r="L28" s="102" t="str">
+        <x:v>终态 + Tween</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" ht="38" customHeight="1">
+      <x:c r="A29" s="103"/>
+      <x:c r="B29" s="103"/>
+      <x:c r="C29" s="103"/>
+      <x:c r="D29" s="103"/>
+      <x:c r="E29" s="103"/>
+      <x:c r="F29" s="103"/>
+      <x:c r="G29" s="103"/>
+      <x:c r="H29" s="103"/>
+      <x:c r="I29" s="103"/>
+      <x:c r="J29" s="103"/>
+      <x:c r="K29" s="103"/>
+      <x:c r="L29" s="103"/>
+    </x:row>
+    <x:row r="30" ht="56" customHeight="1">
+      <x:c r="A30" s="70" t="str">
+        <x:v>Player3D 动作覆盖层 × 组件表现（不新增顶层状态）</x:v>
+      </x:c>
+      <x:c r="B30" s="70"/>
+      <x:c r="C30" s="70"/>
+      <x:c r="D30" s="70"/>
+      <x:c r="E30" s="70"/>
+      <x:c r="F30" s="70"/>
+      <x:c r="G30" s="70"/>
+      <x:c r="H30" s="70"/>
+      <x:c r="I30" s="70"/>
+      <x:c r="J30" s="70"/>
+      <x:c r="K30" s="70"/>
+      <x:c r="L30" s="70"/>
+    </x:row>
+    <x:row r="31" ht="56" customHeight="1">
+      <x:c r="A31" s="70" t="str">
+        <x:v>层级｜状态ID｜中文名｜唯一来源｜退出｜Body｜Head｜Hand L（停用）｜Hand（握持）｜Scarf｜VFX/UI｜首版实现</x:v>
+      </x:c>
+      <x:c r="B31" s="70"/>
+      <x:c r="C31" s="70"/>
+      <x:c r="D31" s="70"/>
+      <x:c r="E31" s="70"/>
+      <x:c r="F31" s="70"/>
+      <x:c r="G31" s="70"/>
+      <x:c r="H31" s="70"/>
+      <x:c r="I31" s="70"/>
+      <x:c r="J31" s="70"/>
+      <x:c r="K31" s="70"/>
+      <x:c r="L31" s="70"/>
+    </x:row>
+    <x:row r="32" ht="56" customHeight="1">
+      <x:c r="A32" s="70" t="str">
         <x:v>叠加</x:v>
       </x:c>
-      <x:c r="B12" s="37" t="str">
-        <x:v>low_health</x:v>
-      </x:c>
-      <x:c r="C12" s="37" t="str">
-        <x:v>低血</x:v>
-      </x:c>
-      <x:c r="D12" s="37" t="str">
-        <x:v>任意存活态</x:v>
-      </x:c>
-      <x:c r="E12" s="37" t="str">
-        <x:v>不改变顶层</x:v>
-      </x:c>
-      <x:c r="F12" s="37" t="str">
-        <x:v>不变</x:v>
-      </x:c>
-      <x:c r="G12" s="37" t="str">
-        <x:v>不变</x:v>
-      </x:c>
-      <x:c r="H12" s="37" t="str">
-        <x:v>保持当前动作</x:v>
-      </x:c>
-      <x:c r="I12" s="37" t="str">
-        <x:v>保持当前动作</x:v>
-      </x:c>
-      <x:c r="J12" s="37" t="str">
-        <x:v>不变</x:v>
-      </x:c>
-      <x:c r="K12" s="37" t="str">
-        <x:v>红色呼吸环</x:v>
-      </x:c>
-      <x:c r="L12" s="37" t="str">
-        <x:v>HP≤30%</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13">
-      <x:c r="A13" s="37" t="str">
+      <x:c r="B32" s="70" t="str">
+        <x:v>firing</x:v>
+      </x:c>
+      <x:c r="C32" s="70" t="str">
+        <x:v>射击</x:v>
+      </x:c>
+      <x:c r="D32" s="70" t="str">
+        <x:v>WeaponModel3D.shot_fired</x:v>
+      </x:c>
+      <x:c r="E32" s="70" t="str">
+        <x:v>短时回弹后退出</x:v>
+      </x:c>
+      <x:c r="F32" s="70" t="str">
+        <x:v>前探/压缩/弹性回弹</x:v>
+      </x:c>
+      <x:c r="G32" s="70" t="str">
+        <x:v>小幅前探</x:v>
+      </x:c>
+      <x:c r="H32" s="70" t="str">
+        <x:v>手枪左手不继承后坐；长枪左手托举并小幅刚性回弹</x:v>
+      </x:c>
+      <x:c r="I32" s="70" t="str">
+        <x:v>右手握把跟随 WeaponSocket；手枪单腕上挑，长枪双手与躯干共同吃后坐</x:v>
+      </x:c>
+      <x:c r="J32" s="70" t="str">
+        <x:v>受冲量轻摆</x:v>
+      </x:c>
+      <x:c r="K32" s="70" t="str">
+        <x:v>枪口闪光/后坐</x:v>
+      </x:c>
+      <x:c r="L32" s="70" t="str">
+        <x:v>真实 shot_fired 信号；WeaponPoseFSM 进入 sidearm_fire/longgun_fire；七种枪体读取独立 fire_style、kick、pitch、roll、lift 参数</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33">
+      <x:c r="A33" s="70" t="str">
         <x:v>叠加</x:v>
       </x:c>
-      <x:c r="B13" s="37" t="str">
-        <x:v>silenced</x:v>
-      </x:c>
-      <x:c r="C13" s="37" t="str">
-        <x:v>沉默</x:v>
-      </x:c>
-      <x:c r="D13" s="37" t="str">
-        <x:v>任意存活态</x:v>
-      </x:c>
-      <x:c r="E13" s="37" t="str">
-        <x:v>不改变顶层</x:v>
-      </x:c>
-      <x:c r="F13" s="37" t="str">
-        <x:v>降饱和可选</x:v>
-      </x:c>
-      <x:c r="G13" s="37" t="str">
-        <x:v>传感器干扰</x:v>
-      </x:c>
-      <x:c r="H13" s="37" t="str">
-        <x:v>保持当前动作</x:v>
-      </x:c>
-      <x:c r="I13" s="37" t="str">
-        <x:v>保持当前动作</x:v>
-      </x:c>
-      <x:c r="J13" s="37" t="str">
-        <x:v>不变</x:v>
-      </x:c>
-      <x:c r="K13" s="37" t="str">
-        <x:v>紫色干扰环</x:v>
-      </x:c>
-      <x:c r="L13" s="37" t="str">
-        <x:v>计时标志</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14">
-      <x:c r="A14" s="37" t="str">
+      <x:c r="B33" s="70" t="str">
+        <x:v>charging</x:v>
+      </x:c>
+      <x:c r="C33" s="70" t="str">
+        <x:v>蓄力</x:v>
+      </x:c>
+      <x:c r="D33" s="70" t="str">
+        <x:v>WeaponModel3D.charge_active / charge_ratio</x:v>
+      </x:c>
+      <x:c r="E33" s="70" t="str">
+        <x:v>释放/取消/换枪/死亡</x:v>
+      </x:c>
+      <x:c r="F33" s="70" t="str">
+        <x:v>下压蓄势</x:v>
+      </x:c>
+      <x:c r="G33" s="70" t="str">
+        <x:v>轻微压低</x:v>
+      </x:c>
+      <x:c r="H33" s="70" t="str">
+        <x:v>长枪左手向内压入形成张力；手枪保持自由手</x:v>
+      </x:c>
+      <x:c r="I33" s="70" t="str">
+        <x:v>右手握把与 WeaponSocket 同相蓄势</x:v>
+      </x:c>
+      <x:c r="J33" s="70" t="str">
+        <x:v>低频张力摆动</x:v>
+      </x:c>
+      <x:c r="K33" s="70" t="str">
+        <x:v>紫色能量提示（可选）</x:v>
+      </x:c>
+      <x:c r="L33" s="70" t="str">
+        <x:v>读取真实蓄力进度；WeaponPoseFSM 进入对应 charge 状态；释放后按枪体 profile 回弹</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" ht="34" customHeight="1">
+      <x:c r="A34" s="102" t="str">
         <x:v>叠加</x:v>
       </x:c>
-      <x:c r="B14" s="37" t="str">
-        <x:v>invincible</x:v>
-      </x:c>
-      <x:c r="C14" s="37" t="str">
-        <x:v>无敌</x:v>
-      </x:c>
-      <x:c r="D14" s="37" t="str">
-        <x:v>dash/hurt</x:v>
-      </x:c>
-      <x:c r="E14" s="37" t="str">
-        <x:v>不改变顶层</x:v>
-      </x:c>
-      <x:c r="F14" s="37" t="str">
-        <x:v>闪烁</x:v>
-      </x:c>
-      <x:c r="G14" s="37" t="str">
-        <x:v>闪烁</x:v>
-      </x:c>
-      <x:c r="H14" s="37" t="str">
-        <x:v>保持当前动作</x:v>
-      </x:c>
-      <x:c r="I14" s="37" t="str">
-        <x:v>保持当前动作</x:v>
-      </x:c>
-      <x:c r="J14" s="37" t="str">
-        <x:v>闪烁</x:v>
-      </x:c>
-      <x:c r="K14" s="37" t="str">
-        <x:v>透明闪烁</x:v>
-      </x:c>
-      <x:c r="L14" s="37" t="str">
-        <x:v>InvincibleTimer 唯一解除</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" ht="56" customHeight="1">
-      <x:c r="A15" s="63" t="str">
-        <x:v>叠加</x:v>
-      </x:c>
-      <x:c r="B15" s="63" t="str">
-        <x:v>reloading</x:v>
-      </x:c>
-      <x:c r="C15" s="63" t="str">
-        <x:v>换弹</x:v>
-      </x:c>
-      <x:c r="D15" s="63" t="str">
-        <x:v>任意持枪存活态</x:v>
-      </x:c>
-      <x:c r="E15" s="63" t="str">
-        <x:v>不改变顶层；完成/取消退出</x:v>
-      </x:c>
-      <x:c r="F15" s="63" t="str">
-        <x:v>保持当前顶层</x:v>
-      </x:c>
-      <x:c r="G15" s="63" t="str">
-        <x:v>保持当前顶层</x:v>
-      </x:c>
-      <x:c r="H15" s="63" t="str">
-        <x:v>手枪左手近身取弹但不计握持；长枪左手离开护木服务</x:v>
-      </x:c>
-      <x:c r="I15" s="63" t="str">
-        <x:v>右手持续握把并跟随 WeaponSocket 下压/回位</x:v>
-      </x:c>
-      <x:c r="J15" s="63" t="str">
-        <x:v>保持当前顶层</x:v>
-      </x:c>
-      <x:c r="K15" s="63" t="str">
-        <x:v>3D头顶billboard进度条；2D弹药栏</x:v>
-      </x:c>
-      <x:c r="L15" s="63" t="str">
-        <x:v>WeaponModel3D 唯一计时源；WeaponPoseFSM 进入 sidearm_reload/longgun_reload；右手保持握把，左手按武器类型服务</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" ht="28" customHeight="1">
-      <x:c r="A16" s="69" t="str">
-        <x:v>Enemy3D 九态状态机 × 模块表现 × 模型轮廓碰撞</x:v>
-      </x:c>
-      <x:c r="B16" s="69"/>
-      <x:c r="C16" s="69"/>
-      <x:c r="D16" s="69"/>
-      <x:c r="E16" s="69"/>
-      <x:c r="F16" s="69"/>
-      <x:c r="G16" s="69"/>
-      <x:c r="H16" s="69"/>
-      <x:c r="I16" s="69"/>
-      <x:c r="J16" s="69"/>
-      <x:c r="K16" s="69"/>
-      <x:c r="L16" s="69"/>
-    </x:row>
-    <x:row r="17" ht="36" customHeight="1">
-      <x:c r="A17" s="63" t="str">
-        <x:v>层级</x:v>
-      </x:c>
-      <x:c r="B17" s="63" t="str">
-        <x:v>状态ID</x:v>
-      </x:c>
-      <x:c r="C17" s="63" t="str">
-        <x:v>中文名</x:v>
-      </x:c>
-      <x:c r="D17" s="63" t="str">
-        <x:v>允许来源</x:v>
-      </x:c>
-      <x:c r="E17" s="63" t="str">
-        <x:v>允许去向</x:v>
-      </x:c>
-      <x:c r="F17" s="63" t="str">
-        <x:v>Core</x:v>
-      </x:c>
-      <x:c r="G17" s="63" t="str">
-        <x:v>Shell</x:v>
-      </x:c>
-      <x:c r="H17" s="63" t="str">
-        <x:v>Appendages</x:v>
-      </x:c>
-      <x:c r="I17" s="63" t="str">
-        <x:v>StateVFX</x:v>
-      </x:c>
-      <x:c r="J17" s="63" t="str">
-        <x:v>行为职责</x:v>
-      </x:c>
-      <x:c r="K17" s="63" t="str">
-        <x:v>验收</x:v>
-      </x:c>
-      <x:c r="L17" s="63" t="str">
-        <x:v>首版实现</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="42" customHeight="1">
-      <x:c r="A18" s="63" t="str">
-        <x:v>顶层</x:v>
-      </x:c>
-      <x:c r="B18" s="63" t="str">
-        <x:v>idle</x:v>
-      </x:c>
-      <x:c r="C18" s="63" t="str">
-        <x:v>待机</x:v>
-      </x:c>
-      <x:c r="D18" s="63" t="str">
-        <x:v>start/patrol/stagger</x:v>
-      </x:c>
-      <x:c r="E18" s="63" t="str">
-        <x:v>patrol/alert/dead</x:v>
-      </x:c>
-      <x:c r="F18" s="63" t="str">
-        <x:v>低频脉冲</x:v>
-      </x:c>
-      <x:c r="G18" s="63" t="str">
-        <x:v>轻浮动</x:v>
-      </x:c>
-      <x:c r="H18" s="63" t="str">
-        <x:v>低速</x:v>
-      </x:c>
-      <x:c r="I18" s="63" t="str">
-        <x:v>关闭</x:v>
-      </x:c>
-      <x:c r="J18" s="63" t="str">
-        <x:v>等待目标</x:v>
-      </x:c>
-      <x:c r="K18" s="63" t="str">
-        <x:v>静态轮廓可读</x:v>
-      </x:c>
-      <x:c r="L18" s="63" t="str">
-        <x:v>模块变换</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="42" customHeight="1">
-      <x:c r="A19" s="63" t="str">
-        <x:v>顶层</x:v>
-      </x:c>
-      <x:c r="B19" s="63" t="str">
-        <x:v>patrol</x:v>
-      </x:c>
-      <x:c r="C19" s="63" t="str">
-        <x:v>巡逻</x:v>
-      </x:c>
-      <x:c r="D19" s="63" t="str">
-        <x:v>idle/search</x:v>
-      </x:c>
-      <x:c r="E19" s="63" t="str">
-        <x:v>idle/alert/stagger/dead</x:v>
-      </x:c>
-      <x:c r="F19" s="63" t="str">
-        <x:v>低频脉冲</x:v>
-      </x:c>
-      <x:c r="G19" s="63" t="str">
-        <x:v>朝巡逻点</x:v>
-      </x:c>
-      <x:c r="H19" s="63" t="str">
-        <x:v>慢速步态</x:v>
-      </x:c>
-      <x:c r="I19" s="63" t="str">
-        <x:v>关闭</x:v>
-      </x:c>
-      <x:c r="J19" s="63" t="str">
-        <x:v>出生点附近巡逻</x:v>
-      </x:c>
-      <x:c r="K19" s="63" t="str">
-        <x:v>无目标不原地僵住</x:v>
-      </x:c>
-      <x:c r="L19" s="63" t="str">
-        <x:v>CharacterBody3D</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" ht="42" customHeight="1">
-      <x:c r="A20" s="63" t="str">
-        <x:v>顶层</x:v>
-      </x:c>
-      <x:c r="B20" s="63" t="str">
-        <x:v>alert</x:v>
-      </x:c>
-      <x:c r="C20" s="63" t="str">
-        <x:v>警觉</x:v>
-      </x:c>
-      <x:c r="D20" s="63" t="str">
-        <x:v>idle/patrol/search</x:v>
-      </x:c>
-      <x:c r="E20" s="63" t="str">
-        <x:v>chase/stagger/dead</x:v>
-      </x:c>
-      <x:c r="F20" s="63" t="str">
-        <x:v>加速</x:v>
-      </x:c>
-      <x:c r="G20" s="63" t="str">
-        <x:v>抬升</x:v>
-      </x:c>
-      <x:c r="H20" s="63" t="str">
-        <x:v>展开</x:v>
-      </x:c>
-      <x:c r="I20" s="63" t="str">
-        <x:v>关闭</x:v>
-      </x:c>
-      <x:c r="J20" s="63" t="str">
-        <x:v>发现玩家</x:v>
-      </x:c>
-      <x:c r="K20" s="63" t="str">
-        <x:v>0.28s响应</x:v>
-      </x:c>
-      <x:c r="L20" s="63" t="str">
-        <x:v>模块变换</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" ht="42" customHeight="1">
-      <x:c r="A21" s="63" t="str">
-        <x:v>顶层</x:v>
-      </x:c>
-      <x:c r="B21" s="63" t="str">
-        <x:v>chase</x:v>
-      </x:c>
-      <x:c r="C21" s="63" t="str">
-        <x:v>追击</x:v>
-      </x:c>
-      <x:c r="D21" s="63" t="str">
-        <x:v>alert/attack/stagger</x:v>
-      </x:c>
-      <x:c r="E21" s="63" t="str">
-        <x:v>search/telegraph/stagger/dead</x:v>
-      </x:c>
-      <x:c r="F21" s="63" t="str">
-        <x:v>稳定</x:v>
-      </x:c>
-      <x:c r="G21" s="63" t="str">
-        <x:v>朝目标</x:v>
-      </x:c>
-      <x:c r="H21" s="63" t="str">
-        <x:v>步态</x:v>
-      </x:c>
-      <x:c r="I21" s="63" t="str">
-        <x:v>关闭</x:v>
-      </x:c>
-      <x:c r="J21" s="63" t="str">
-        <x:v>距离控制</x:v>
-      </x:c>
-      <x:c r="K21" s="63" t="str">
-        <x:v>七类速度差</x:v>
-      </x:c>
-      <x:c r="L21" s="63" t="str">
-        <x:v>CharacterBody3D</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" ht="42" customHeight="1">
-      <x:c r="A22" s="63" t="str">
-        <x:v>顶层</x:v>
-      </x:c>
-      <x:c r="B22" s="63" t="str">
-        <x:v>search</x:v>
-      </x:c>
-      <x:c r="C22" s="63" t="str">
-        <x:v>搜索</x:v>
-      </x:c>
-      <x:c r="D22" s="63" t="str">
-        <x:v>chase</x:v>
-      </x:c>
-      <x:c r="E22" s="63" t="str">
-        <x:v>patrol/alert/stagger/dead</x:v>
-      </x:c>
-      <x:c r="F22" s="63" t="str">
-        <x:v>渐缓</x:v>
-      </x:c>
-      <x:c r="G22" s="63" t="str">
-        <x:v>朝最后位置</x:v>
-      </x:c>
-      <x:c r="H22" s="63" t="str">
-        <x:v>搜索步态</x:v>
-      </x:c>
-      <x:c r="I22" s="63" t="str">
-        <x:v>搜索提示</x:v>
-      </x:c>
-      <x:c r="J22" s="63" t="str">
-        <x:v>失去视线后搜索</x:v>
-      </x:c>
-      <x:c r="K22" s="63" t="str">
-        <x:v>2.4s后回巡逻</x:v>
-      </x:c>
-      <x:c r="L22" s="63" t="str">
-        <x:v>射线+最后位置</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23" ht="42" customHeight="1">
-      <x:c r="A23" s="63" t="str">
-        <x:v>顶层</x:v>
-      </x:c>
-      <x:c r="B23" s="63" t="str">
-        <x:v>telegraph</x:v>
-      </x:c>
-      <x:c r="C23" s="63" t="str">
-        <x:v>预警</x:v>
-      </x:c>
-      <x:c r="D23" s="63" t="str">
-        <x:v>chase</x:v>
-      </x:c>
-      <x:c r="E23" s="63" t="str">
-        <x:v>attack/stagger/dead</x:v>
-      </x:c>
-      <x:c r="F23" s="63" t="str">
-        <x:v>高频脉冲</x:v>
-      </x:c>
-      <x:c r="G23" s="63" t="str">
-        <x:v>稳定</x:v>
-      </x:c>
-      <x:c r="H23" s="63" t="str">
-        <x:v>蓄势</x:v>
-      </x:c>
-      <x:c r="I23" s="63" t="str">
-        <x:v>红色预警环</x:v>
-      </x:c>
-      <x:c r="J23" s="63" t="str">
-        <x:v>攻击前摇</x:v>
-      </x:c>
-      <x:c r="K23" s="63" t="str">
-        <x:v>不可省略</x:v>
-      </x:c>
-      <x:c r="L23" s="63" t="str">
-        <x:v>计时状态</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24" ht="42" customHeight="1">
-      <x:c r="A24" s="63" t="str">
-        <x:v>顶层</x:v>
-      </x:c>
-      <x:c r="B24" s="63" t="str">
-        <x:v>attack</x:v>
-      </x:c>
-      <x:c r="C24" s="63" t="str">
-        <x:v>攻击</x:v>
-      </x:c>
-      <x:c r="D24" s="63" t="str">
-        <x:v>telegraph</x:v>
-      </x:c>
-      <x:c r="E24" s="63" t="str">
-        <x:v>chase/stagger/dead</x:v>
-      </x:c>
-      <x:c r="F24" s="63" t="str">
-        <x:v>峰值</x:v>
-      </x:c>
-      <x:c r="G24" s="63" t="str">
-        <x:v>反冲</x:v>
-      </x:c>
-      <x:c r="H24" s="63" t="str">
-        <x:v>执行</x:v>
-      </x:c>
-      <x:c r="I24" s="63" t="str">
-        <x:v>按攻击类型</x:v>
-      </x:c>
-      <x:c r="J24" s="63" t="str">
-        <x:v>近战/远程/召唤/爆炸</x:v>
-      </x:c>
-      <x:c r="K24" s="63" t="str">
-        <x:v>七类差异</x:v>
-      </x:c>
-      <x:c r="L24" s="63" t="str">
-        <x:v>profile策略</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25">
-      <x:c r="A25" t="str">
-        <x:v>顶层</x:v>
-      </x:c>
-      <x:c r="B25" t="str">
-        <x:v>stagger</x:v>
-      </x:c>
-      <x:c r="C25" t="str">
-        <x:v>硬直</x:v>
-      </x:c>
-      <x:c r="D25" t="str">
-        <x:v>任意存活态</x:v>
-      </x:c>
-      <x:c r="E25" t="str">
-        <x:v>chase/dead</x:v>
-      </x:c>
-      <x:c r="F25" t="str">
-        <x:v>闪色</x:v>
-      </x:c>
-      <x:c r="G25" t="str">
-        <x:v>冲击</x:v>
-      </x:c>
-      <x:c r="H25" t="str">
-        <x:v>暂停</x:v>
-      </x:c>
-      <x:c r="I25" t="str">
-        <x:v>伤害反馈</x:v>
-      </x:c>
-      <x:c r="J25" t="str">
-        <x:v>受击窗口</x:v>
-      </x:c>
-      <x:c r="K25" t="str">
-        <x:v>方向可读</x:v>
-      </x:c>
-      <x:c r="L25" t="str">
-        <x:v>统一伤害入口</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="26">
-      <x:c r="A26" t="str">
-        <x:v>顶层</x:v>
-      </x:c>
-      <x:c r="B26" t="str">
-        <x:v>dead</x:v>
-      </x:c>
-      <x:c r="C26" t="str">
-        <x:v>死亡</x:v>
-      </x:c>
-      <x:c r="D26" t="str">
-        <x:v>任意存活态</x:v>
-      </x:c>
-      <x:c r="E26" t="str">
-        <x:v>无（终态）</x:v>
-      </x:c>
-      <x:c r="F26" t="str">
-        <x:v>熄灭</x:v>
-      </x:c>
-      <x:c r="G26" t="str">
-        <x:v>压扁</x:v>
-      </x:c>
-      <x:c r="H26" t="str">
-        <x:v>停止</x:v>
-      </x:c>
-      <x:c r="I26" t="str">
-        <x:v>爆散/淡出</x:v>
-      </x:c>
-      <x:c r="J26" t="str">
-        <x:v>掉落与计数</x:v>
-      </x:c>
-      <x:c r="K26" t="str">
-        <x:v>不可回存活态</x:v>
-      </x:c>
-      <x:c r="L26" t="str">
-        <x:v>终态 + Tween</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="28" ht="38" customHeight="1">
-      <x:c r="A28" s="81" t="str">
-        <x:v>Player3D 动作覆盖层 × 组件表现（不新增顶层状态）</x:v>
-      </x:c>
-      <x:c r="B28" s="81"/>
-      <x:c r="C28" s="81"/>
-      <x:c r="D28" s="81"/>
-      <x:c r="E28" s="81"/>
-      <x:c r="F28" s="81"/>
-      <x:c r="G28" s="81"/>
-      <x:c r="H28" s="81"/>
-      <x:c r="I28" s="81"/>
-      <x:c r="J28" s="81"/>
-      <x:c r="K28" s="81"/>
-      <x:c r="L28" s="81"/>
-    </x:row>
-    <x:row r="29" ht="38" customHeight="1">
-      <x:c r="A29" s="82" t="str">
-        <x:v>层级｜状态ID｜中文名｜唯一来源｜退出｜Body｜Head｜Hand L（停用）｜Hand（握持）｜Scarf｜VFX/UI｜首版实现</x:v>
-      </x:c>
-      <x:c r="B29" s="82"/>
-      <x:c r="C29" s="82"/>
-      <x:c r="D29" s="82"/>
-      <x:c r="E29" s="82"/>
-      <x:c r="F29" s="82"/>
-      <x:c r="G29" s="82"/>
-      <x:c r="H29" s="82"/>
-      <x:c r="I29" s="82"/>
-      <x:c r="J29" s="82"/>
-      <x:c r="K29" s="82"/>
-      <x:c r="L29" s="82"/>
-    </x:row>
-    <x:row r="30" ht="56" customHeight="1">
-      <x:c r="A30" s="63" t="str">
-        <x:v>叠加</x:v>
-      </x:c>
-      <x:c r="B30" s="63" t="str">
-        <x:v>firing</x:v>
-      </x:c>
-      <x:c r="C30" s="63" t="str">
-        <x:v>射击</x:v>
-      </x:c>
-      <x:c r="D30" s="63" t="str">
-        <x:v>WeaponModel3D.shot_fired</x:v>
-      </x:c>
-      <x:c r="E30" s="63" t="str">
-        <x:v>短时回弹后退出</x:v>
-      </x:c>
-      <x:c r="F30" s="63" t="str">
-        <x:v>前探/压缩/弹性回弹</x:v>
-      </x:c>
-      <x:c r="G30" s="63" t="str">
-        <x:v>小幅前探</x:v>
-      </x:c>
-      <x:c r="H30" s="63" t="str">
-        <x:v>手枪左手不继承后坐；长枪左手托举并小幅刚性回弹</x:v>
-      </x:c>
-      <x:c r="I30" s="63" t="str">
-        <x:v>右手握把跟随 WeaponSocket；手枪单腕上挑，长枪双手与躯干共同吃后坐</x:v>
-      </x:c>
-      <x:c r="J30" s="63" t="str">
-        <x:v>受冲量轻摆</x:v>
-      </x:c>
-      <x:c r="K30" s="63" t="str">
-        <x:v>枪口闪光/后坐</x:v>
-      </x:c>
-      <x:c r="L30" s="63" t="str">
-        <x:v>真实 shot_fired 信号；WeaponPoseFSM 进入 sidearm_fire/longgun_fire；七种枪体读取独立 fire_style、kick、pitch、roll、lift 参数</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="31" ht="56" customHeight="1">
-      <x:c r="A31" s="63" t="str">
-        <x:v>叠加</x:v>
-      </x:c>
-      <x:c r="B31" s="63" t="str">
-        <x:v>charging</x:v>
-      </x:c>
-      <x:c r="C31" s="63" t="str">
-        <x:v>蓄力</x:v>
-      </x:c>
-      <x:c r="D31" s="63" t="str">
-        <x:v>WeaponModel3D.charge_active / charge_ratio</x:v>
-      </x:c>
-      <x:c r="E31" s="63" t="str">
-        <x:v>释放/取消/换枪/死亡</x:v>
-      </x:c>
-      <x:c r="F31" s="63" t="str">
-        <x:v>下压蓄势</x:v>
-      </x:c>
-      <x:c r="G31" s="63" t="str">
-        <x:v>轻微压低</x:v>
-      </x:c>
-      <x:c r="H31" s="63" t="str">
-        <x:v>长枪左手向内压入形成张力；手枪保持自由手</x:v>
-      </x:c>
-      <x:c r="I31" s="63" t="str">
-        <x:v>右手握把与 WeaponSocket 同相蓄势</x:v>
-      </x:c>
-      <x:c r="J31" s="63" t="str">
-        <x:v>低频张力摆动</x:v>
-      </x:c>
-      <x:c r="K31" s="63" t="str">
-        <x:v>紫色能量提示（可选）</x:v>
-      </x:c>
-      <x:c r="L31" s="63" t="str">
-        <x:v>读取真实蓄力进度；WeaponPoseFSM 进入对应 charge 状态；释放后按枪体 profile 回弹</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="32" ht="56" customHeight="1">
-      <x:c r="A32" s="63" t="str">
-        <x:v>叠加</x:v>
-      </x:c>
-      <x:c r="B32" s="63" t="str">
+      <x:c r="B34" s="102" t="str">
         <x:v>knockback</x:v>
       </x:c>
-      <x:c r="C32" s="63" t="str">
+      <x:c r="C34" s="102" t="str">
         <x:v>受击击飞</x:v>
       </x:c>
-      <x:c r="D32" s="63" t="str">
+      <x:c r="D34" s="102" t="str">
         <x:v>Player3D 命中方向/强度/时长</x:v>
       </x:c>
-      <x:c r="E32" s="63" t="str">
+      <x:c r="E34" s="102" t="str">
         <x:v>冲量归零或死亡</x:v>
       </x:c>
-      <x:c r="F32" s="63" t="str">
+      <x:c r="F34" s="102" t="str">
         <x:v>反向位移/压缩/弹回</x:v>
       </x:c>
-      <x:c r="G32" s="63" t="str">
+      <x:c r="G34" s="102" t="str">
         <x:v>夸张后仰甩头/回正</x:v>
       </x:c>
-      <x:c r="H32" s="63" t="str">
+      <x:c r="H34" s="102" t="str">
         <x:v>手枪自由左手外甩；长枪左手回护木</x:v>
       </x:c>
-      <x:c r="I32" s="63" t="str">
+      <x:c r="I34" s="102" t="str">
         <x:v>右手与 WeaponSocket 同相后退/回正</x:v>
       </x:c>
-      <x:c r="J32" s="63" t="str">
+      <x:c r="J34" s="102" t="str">
         <x:v>滞后甩动</x:v>
       </x:c>
-      <x:c r="K32" s="63" t="str">
+      <x:c r="K34" s="102" t="str">
         <x:v>红闪/短轨迹</x:v>
       </x:c>
-      <x:c r="L32" s="63" t="str">
+      <x:c r="L34" s="102" t="str">
         <x:v>hurt 消费递减XZ冲量；双耳/双脚/双手分层过冲，不新增顶层状态</x:v>
       </x:c>
     </x:row>
-    <x:row r="34" ht="34" customHeight="1">
-      <x:c r="A34" s="93" t="str">
-        <x:v>Player3D DIY 外观槽 × 动态继承（不影响六态/玩法）</x:v>
-      </x:c>
-      <x:c r="B34" s="93"/>
-      <x:c r="C34" s="93"/>
-      <x:c r="D34" s="93"/>
-      <x:c r="E34" s="93"/>
-      <x:c r="F34" s="93"/>
-      <x:c r="G34" s="93"/>
-      <x:c r="H34" s="93"/>
-      <x:c r="I34" s="93"/>
-      <x:c r="J34" s="93"/>
-      <x:c r="K34" s="93"/>
-      <x:c r="L34" s="93"/>
-    </x:row>
     <x:row r="35" ht="34" customHeight="1">
-      <x:c r="A35" s="94" t="str">
+      <x:c r="A35" s="103"/>
+      <x:c r="B35" s="103"/>
+      <x:c r="C35" s="103"/>
+      <x:c r="D35" s="103"/>
+      <x:c r="E35" s="103"/>
+      <x:c r="F35" s="103"/>
+      <x:c r="G35" s="103"/>
+      <x:c r="H35" s="103"/>
+      <x:c r="I35" s="103"/>
+      <x:c r="J35" s="103"/>
+      <x:c r="K35" s="103"/>
+      <x:c r="L35" s="103"/>
+    </x:row>
+    <x:row r="36" ht="34" customHeight="1">
+      <x:c r="A36" s="70" t="str">
+        <x:v>Player3D DIY 外观槽 × 动态继承（不影响八态/玩法）</x:v>
+      </x:c>
+      <x:c r="B36" s="70"/>
+      <x:c r="C36" s="70"/>
+      <x:c r="D36" s="70"/>
+      <x:c r="E36" s="70"/>
+      <x:c r="F36" s="70"/>
+      <x:c r="G36" s="70"/>
+      <x:c r="H36" s="70"/>
+      <x:c r="I36" s="70"/>
+      <x:c r="J36" s="70"/>
+      <x:c r="K36" s="70"/>
+      <x:c r="L36" s="70"/>
+    </x:row>
+    <x:row r="37">
+      <x:c r="A37" s="70" t="str">
         <x:v>槽位｜候选变体｜父组件｜移动｜射击/蓄力｜受击/击飞｜换弹｜死亡｜挂点契约｜验收｜复用范围｜首版实现</x:v>
       </x:c>
-      <x:c r="B35" s="94"/>
-      <x:c r="C35" s="94"/>
-      <x:c r="D35" s="94"/>
-      <x:c r="E35" s="94"/>
-      <x:c r="F35" s="94"/>
-      <x:c r="G35" s="94"/>
-      <x:c r="H35" s="94"/>
-      <x:c r="I35" s="94"/>
-      <x:c r="J35" s="94"/>
-      <x:c r="K35" s="94"/>
-      <x:c r="L35" s="94"/>
-    </x:row>
-    <x:row r="36" ht="34" customHeight="1">
-      <x:c r="A36" s="63" t="str">
+      <x:c r="B37" s="70"/>
+      <x:c r="C37" s="70"/>
+      <x:c r="D37" s="70"/>
+      <x:c r="E37" s="70"/>
+      <x:c r="F37" s="70"/>
+      <x:c r="G37" s="70"/>
+      <x:c r="H37" s="70"/>
+      <x:c r="I37" s="70"/>
+      <x:c r="J37" s="70"/>
+      <x:c r="K37" s="70"/>
+      <x:c r="L37" s="70"/>
+    </x:row>
+    <x:row r="38" ht="38" customHeight="1">
+      <x:c r="A38" s="70" t="str">
         <x:v>body/head/hand/feet/hat/glasses</x:v>
       </x:c>
-      <x:c r="B36" s="63" t="str">
+      <x:c r="B38" s="70" t="str">
         <x:v>4+4+4+4+3+3</x:v>
       </x:c>
-      <x:c r="C36" s="63" t="str">
+      <x:c r="C38" s="70" t="str">
         <x:v>Body/Head/Hand/Feet/Wearables</x:v>
       </x:c>
-      <x:c r="D36" s="63" t="str">
+      <x:c r="D38" s="70" t="str">
         <x:v>身体弹性+双脚交替+圆短尾轻摆</x:v>
       </x:c>
-      <x:c r="E36" s="63" t="str">
+      <x:c r="E38" s="70" t="str">
         <x:v>手/枪同相后坐；头前探</x:v>
       </x:c>
-      <x:c r="F36" s="63" t="str">
+      <x:c r="F38" s="70" t="str">
         <x:v>整体后仰/脚随根回正</x:v>
       </x:c>
-      <x:c r="G36" s="63" t="str">
+      <x:c r="G38" s="70" t="str">
         <x:v>Hand+Socket同相</x:v>
       </x:c>
-      <x:c r="H36" s="63" t="str">
+      <x:c r="H38" s="70" t="str">
         <x:v>四主模块随根倾倒</x:v>
       </x:c>
-      <x:c r="I36" s="63" t="str">
+      <x:c r="I38" s="70" t="str">
         <x:v>唯一手/挂点相对向量固定</x:v>
       </x:c>
-      <x:c r="J36" s="63" t="str">
-        <x:v>四主模块+双眼双耳短尾+六态覆盖</x:v>
-      </x:c>
-      <x:c r="K36" s="63" t="str">
+      <x:c r="J38" s="70" t="str">
+        <x:v>四主模块+双眼双耳短尾+八态覆盖</x:v>
+      </x:c>
+      <x:c r="K38" s="70" t="str">
         <x:v>3D玩家/预览场</x:v>
       </x:c>
-      <x:c r="L36" s="63" t="str">
+      <x:c r="L38" s="70" t="str">
         <x:v>Godot原生方体/三角耳/圆尾；Player3D.set_avatar_customization</x:v>
       </x:c>
     </x:row>
-    <x:row r="38" ht="38" customHeight="1">
-      <x:c r="A38" s="63" t="str">
+    <x:row r="39" ht="38" customHeight="1">
+      <x:c r="A39" s="70"/>
+      <x:c r="B39" s="70"/>
+      <x:c r="C39" s="70"/>
+      <x:c r="D39" s="70"/>
+      <x:c r="E39" s="70"/>
+      <x:c r="F39" s="70"/>
+      <x:c r="G39" s="70"/>
+      <x:c r="H39" s="70"/>
+      <x:c r="I39" s="70"/>
+      <x:c r="J39" s="70"/>
+      <x:c r="K39" s="70"/>
+      <x:c r="L39" s="70"/>
+    </x:row>
+    <x:row r="40" ht="38" customHeight="1">
+      <x:c r="A40" s="70" t="str">
         <x:v>PH33 方形猫子组件 × 动作归属（不新增状态）</x:v>
       </x:c>
-      <x:c r="B38" s="63"/>
-      <x:c r="C38" s="63"/>
-      <x:c r="D38" s="63"/>
-      <x:c r="E38" s="63"/>
-      <x:c r="F38" s="63"/>
-      <x:c r="G38" s="63"/>
-      <x:c r="H38" s="63"/>
-      <x:c r="I38" s="63"/>
-      <x:c r="J38" s="63"/>
-      <x:c r="K38" s="63"/>
-      <x:c r="L38" s="63"/>
-    </x:row>
-    <x:row r="39" ht="38" customHeight="1">
-      <x:c r="A39" s="63" t="str">
+      <x:c r="B40" s="70"/>
+      <x:c r="C40" s="70"/>
+      <x:c r="D40" s="70"/>
+      <x:c r="E40" s="70"/>
+      <x:c r="F40" s="70"/>
+      <x:c r="G40" s="70"/>
+      <x:c r="H40" s="70"/>
+      <x:c r="I40" s="70"/>
+      <x:c r="J40" s="70"/>
+      <x:c r="K40" s="70"/>
+      <x:c r="L40" s="70"/>
+    </x:row>
+    <x:row r="41">
+      <x:c r="A41" s="70" t="str">
         <x:v>父模块｜子组件｜节点数量｜Idle｜Moving｜Dashing｜Hurt/Knockback｜Reload/Fire｜Dead｜图形语言｜禁止事项｜验收</x:v>
       </x:c>
-      <x:c r="B39" s="63"/>
-      <x:c r="C39" s="63"/>
-      <x:c r="D39" s="63"/>
-      <x:c r="E39" s="63"/>
-      <x:c r="F39" s="63"/>
-      <x:c r="G39" s="63"/>
-      <x:c r="H39" s="63"/>
-      <x:c r="I39" s="63"/>
-      <x:c r="J39" s="63"/>
-      <x:c r="K39" s="63"/>
-      <x:c r="L39" s="63"/>
-    </x:row>
-    <x:row r="40" ht="38" customHeight="1">
-      <x:c r="A40" s="63" t="str">
+      <x:c r="B41" s="70"/>
+      <x:c r="C41" s="70"/>
+      <x:c r="D41" s="70"/>
+      <x:c r="E41" s="70"/>
+      <x:c r="F41" s="70"/>
+      <x:c r="G41" s="70"/>
+      <x:c r="H41" s="70"/>
+      <x:c r="I41" s="70"/>
+      <x:c r="J41" s="70"/>
+      <x:c r="K41" s="70"/>
+      <x:c r="L41" s="70"/>
+    </x:row>
+    <x:row r="42">
+      <x:c r="A42" s="70" t="str">
         <x:v>Head / Body / Feet</x:v>
       </x:c>
-      <x:c r="B40" s="63" t="str">
+      <x:c r="B42" s="70" t="str">
         <x:v>Eyes / Ears / TailStub / FootL / FootR</x:v>
       </x:c>
-      <x:c r="C40" s="63" t="str">
+      <x:c r="C42" s="70" t="str">
         <x:v>2 / 2 / 1 / 2</x:v>
       </x:c>
-      <x:c r="D40" s="63" t="str">
+      <x:c r="D42" s="70" t="str">
         <x:v>双眼双耳稳定；短尾微摆</x:v>
       </x:c>
-      <x:c r="E40" s="63" t="str">
+      <x:c r="E42" s="70" t="str">
         <x:v>双脚交替抬起；短尾轻摆</x:v>
       </x:c>
-      <x:c r="F40" s="63" t="str">
+      <x:c r="F42" s="70" t="str">
         <x:v>随VisualRoot压缩</x:v>
       </x:c>
-      <x:c r="G40" s="63" t="str">
+      <x:c r="G42" s="70" t="str">
         <x:v>随父模块后仰回正</x:v>
       </x:c>
-      <x:c r="H40" s="63" t="str">
+      <x:c r="H42" s="70" t="str">
         <x:v>手/枪动作不牵动脚；头部继承</x:v>
       </x:c>
-      <x:c r="I40" s="63" t="str">
+      <x:c r="I42" s="70" t="str">
         <x:v>随父模块倾倒</x:v>
       </x:c>
-      <x:c r="J40" s="63" t="str">
+      <x:c r="J42" s="70" t="str">
         <x:v>方头方身方手方脚；圆尾唯一例外</x:v>
       </x:c>
-      <x:c r="K40" s="63" t="str">
+      <x:c r="K42" s="70" t="str">
         <x:v>嘴/鼻/第二手/长尾/烘焙跨模块</x:v>
       </x:c>
-      <x:c r="L40" s="63" t="str">
+      <x:c r="L42" s="70" t="str">
         <x:v>节点路径+数量+步态+持枪+视觉</x:v>
       </x:c>
     </x:row>
@@ -15272,13 +15875,13 @@
   <x:mergeCells>
     <x:mergeCell ref="A1:L2"/>
     <x:mergeCell ref="A3:L3"/>
-    <x:mergeCell ref="A16:L16"/>
-    <x:mergeCell ref="A28:L28"/>
-    <x:mergeCell ref="A29:L29"/>
-    <x:mergeCell ref="A34:L34"/>
-    <x:mergeCell ref="A35:L35"/>
-    <x:mergeCell ref="A38:L38"/>
-    <x:mergeCell ref="A39:L39"/>
+    <x:mergeCell ref="A18:L18"/>
+    <x:mergeCell ref="A30:L30"/>
+    <x:mergeCell ref="A31:L31"/>
+    <x:mergeCell ref="A36:L36"/>
+    <x:mergeCell ref="A37:L37"/>
+    <x:mergeCell ref="A40:L40"/>
+    <x:mergeCell ref="A41:L41"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -16737,6 +17340,259 @@
         <x:v>Codex</x:v>
       </x:c>
     </x:row>
+    <x:row r="22" ht="72" customHeight="1">
+      <x:c r="A22" s="63" t="str">
+        <x:v>v1.16</x:v>
+      </x:c>
+      <x:c r="B22" s="64" t="n">
+        <x:v>46232</x:v>
+      </x:c>
+      <x:c r="C22" s="63" t="str">
+        <x:v>塔楼Blender三层堆叠版登记</x:v>
+      </x:c>
+      <x:c r="D22" s="63" t="str">
+        <x:v>ENV-TOWER-DESCENT-KIT-3D</x:v>
+      </x:c>
+      <x:c r="E22" s="63" t="str">
+        <x:v>将旧v001横向组件评审板保留为历史版本；登记独立v002三层真实堆叠文件，含楼板、外墙、室内隔墙、15扇门及西/东两段实际楼梯，并修复同名文件覆盖导致的评审图不一致。</x:v>
+      </x:c>
+      <x:c r="F22" s="63" t="str">
+        <x:v>AssetID不变；只升级Blender评审源文件版本；确认前不导出GLB、不接入Godot。</x:v>
+      </x:c>
+      <x:c r="G22" s="63" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" ht="78" customHeight="1">
+      <x:c r="A23" s="63" t="str">
+        <x:v>v1.17</x:v>
+      </x:c>
+      <x:c r="B23" s="64" t="n">
+        <x:v>46233</x:v>
+      </x:c>
+      <x:c r="C23" s="63" t="str">
+        <x:v>塔楼双楼梯与五倍边长地图登记</x:v>
+      </x:c>
+      <x:c r="D23" s="63" t="str">
+        <x:v>ENV-TOWER-DESCENT-KIT-3D</x:v>
+      </x:c>
+      <x:c r="E23" s="63" t="str">
+        <x:v>将用户手工v003保存为快照；登记v004特殊楼顶梯与通用旋转梯、02_STAIRWELLS集合层级、核心门口连接板、335.410m总占地、67.082m中央核心和空外围楼板。</x:v>
+      </x:c>
+      <x:c r="F23" s="63" t="str">
+        <x:v>AssetID不变；v003可回退；只升级Blender评审源文件，确认前不导出GLB、不接入Godot。</x:v>
+      </x:c>
+      <x:c r="G23" s="63" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" ht="100" customHeight="1">
+      <x:c r="A24" s="63" t="str">
+        <x:v>v1.18</x:v>
+      </x:c>
+      <x:c r="B24" s="64" t="n">
+        <x:v>46233</x:v>
+      </x:c>
+      <x:c r="C24" s="63" t="str">
+        <x:v>塔楼整层外壳五倍边长修正</x:v>
+      </x:c>
+      <x:c r="D24" s="63" t="str">
+        <x:v>ENV-TOWER-DESCENT-KIT-3D</x:v>
+      </x:c>
+      <x:c r="E24" s="63" t="str">
+        <x:v>登记v005：楼顶女儿墙、基地外墙、战斗层外墙全部移到335.410m总楼层边界；旧核心满高外墙取消，67.082m中央核心、楼梯、门、设施和内部隔墙保持原尺寸。</x:v>
+      </x:c>
+      <x:c r="F24" s="63" t="str">
+        <x:v>AssetID不变；v004可回退；只修正Blender评审母版，确认前不导出GLB、不接入Godot。</x:v>
+      </x:c>
+      <x:c r="G24" s="63" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" ht="115" customHeight="1">
+      <x:c r="A25" s="63" t="str">
+        <x:v>v1.19</x:v>
+      </x:c>
+      <x:c r="B25" s="64" t="n">
+        <x:v>46233</x:v>
+      </x:c>
+      <x:c r="C25" s="63" t="str">
+        <x:v>塔楼五米模块化楼层与墙体</x:v>
+      </x:c>
+      <x:c r="D25" s="63" t="str">
+        <x:v>ENV-TOWER-DESCENT-KIT-3D; ENV-TOWER-FLOOR-TILE-5M; ENV-TOWER-WALL-SOLID-5M; ENV-TOWER-WALL-PARAPET-5M; ENV-TOWER-WALL-DOOR-5M</x:v>
+      </x:c>
+      <x:c r="E25" s="63" t="str">
+        <x:v>登记v006：335m整层与65m基地/战斗核心全部对齐5m网格；地砖、满高墙、楼顶女儿墙、带门墙成为四个稳定子资产，基地完整围合，战斗内墙和门可独立拼装。</x:v>
+      </x:c>
+      <x:c r="F25" s="63" t="str">
+        <x:v>v005用户内存状态另存快照；楼梯手调结构不重做。四个子资产当前仅为Blender程序占位，未导出GLB、未接入Godot。</x:v>
+      </x:c>
+      <x:c r="G25" s="63" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" ht="118" customHeight="1">
+      <x:c r="A26" s="70" t="str">
+        <x:v>v1.20</x:v>
+      </x:c>
+      <x:c r="B26" s="71" t="n">
+        <x:v>46233</x:v>
+      </x:c>
+      <x:c r="C26" s="70" t="str">
+        <x:v>塔楼5m GLB与99—95层Godot首批关卡接入</x:v>
+      </x:c>
+      <x:c r="D26" s="70" t="str">
+        <x:v>ENV-TOWER-DESCENT-KIT-3D及四个5m子资产</x:v>
+      </x:c>
+      <x:c r="E26" s="70" t="str">
+        <x:v>四个Blender模块导出独立GLB并接入335m楼顶、99层基地、98—95层五房+电梯探索关卡；登记9m双跑楼梯、门后命运、Boss/撤离、城市日照、智能剖切与≤5层流送验收。</x:v>
+      </x:c>
+      <x:c r="F26" s="70" t="str">
+        <x:v>AssetID与v006 Blender母版不变；子资产状态由程序占位升级为原型已接入；旧四主题Dungeon3D玩法继续共用。</x:v>
+      </x:c>
+      <x:c r="G26" s="70" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" ht="118" customHeight="1">
+      <x:c r="A27" s="70" t="str">
+        <x:v>v1.21</x:v>
+      </x:c>
+      <x:c r="B27" s="71" t="n">
+        <x:v>46233</x:v>
+      </x:c>
+      <x:c r="C27" s="70" t="str">
+        <x:v>Blender楼梯直入与99—95层种子化关卡</x:v>
+      </x:c>
+      <x:c r="D27" s="70" t="str">
+        <x:v>ENV-TOWER-DESCENT-KIT-3D; ENV-TOWER-STAIRWELL-GENERIC-9M; ENV-TOWER-STAIRWELL-ROOFTOP-9M</x:v>
+      </x:c>
+      <x:c r="E27" s="70" t="str">
+        <x:v>两套用户手调楼梯从v006根节点直接导出GLB并接入Godot；登记前三段门禁差异、四类种子化房间模板、固定电梯、95层Boss、城市/室内光、智能遮挡与≤5层流送。</x:v>
+      </x:c>
+      <x:c r="F27" s="70" t="str">
+        <x:v>新增两个楼梯子AssetID，不复制程序踏步；四个5m模块ID和母版ID不变；运行时碰撞/吸附与Blender视觉职责分离。</x:v>
+      </x:c>
+      <x:c r="G27" s="70" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" ht="118" customHeight="1">
+      <x:c r="A28" s="70" t="str">
+        <x:v>v1.22</x:v>
+      </x:c>
+      <x:c r="B28" s="71" t="n">
+        <x:v>46233</x:v>
+      </x:c>
+      <x:c r="C28" s="70" t="str">
+        <x:v>bunny01完整视觉与碰撞统一为1米</x:v>
+      </x:c>
+      <x:c r="D28" s="70" t="str">
+        <x:v>CHR-PLY-CAPSULE01-3D-BUNNY01及六个稳定组件AssetID</x:v>
+      </x:c>
+      <x:c r="E28" s="70" t="str">
+        <x:v>从v004派生真实1m Blender v005与七个pivot-local GLB；Godot改用v005装配，碰撞体高1m，持枪视觉、挂点、可穿戴、VFX和全部米制动作平移同步缩放。</x:v>
+      </x:c>
+      <x:c r="F28" s="70" t="str">
+        <x:v>不新增角色AssetID；v004保留回退。静态AABB、六态、武器姿势、碰撞、DIY、换弹、塔楼与性能验收通过。</x:v>
+      </x:c>
+      <x:c r="G28" s="70" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" ht="84" hidden="0" customHeight="1">
+      <x:c r="A29" s="70" t="str">
+        <x:v>v1.23</x:v>
+      </x:c>
+      <x:c r="B29" s="71" t="n">
+        <x:v>46233</x:v>
+      </x:c>
+      <x:c r="C29" s="70" t="str">
+        <x:v>bunny01正式定版为1.5米</x:v>
+      </x:c>
+      <x:c r="D29" s="70" t="str">
+        <x:v>CHR-PLY-CAPSULE01-3D-BUNNY01及六个稳定组件AssetID</x:v>
+      </x:c>
+      <x:c r="E29" s="70" t="str">
+        <x:v>从一米v005等比烘焙真实1.5m Blender v006、七个pivot-local GLB与Godot v006装配；取消Avatar3D临时1.5倍缩放，碰撞、挂点、附件与米制动画固定为1.5m契约。</x:v>
+      </x:c>
+      <x:c r="F29" s="70" t="str">
+        <x:v>不新增AssetID；v005保留回退。Blender/Godot AABB、武器姿势、碰撞、六态、DIY、换弹、塔楼楼梯和PH40镜头验收通过。</x:v>
+      </x:c>
+      <x:c r="G29" s="70" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" ht="118" customHeight="1">
+      <x:c r="A30" s="70" t="str">
+        <x:v>v1.24</x:v>
+      </x:c>
+      <x:c r="B30" s="71" t="n">
+        <x:v>46233</x:v>
+      </x:c>
+      <x:c r="C30" s="70" t="str">
+        <x:v>PH43楼梯承重、下落落地与屋顶可读性</x:v>
+      </x:c>
+      <x:c r="D30" s="70" t="str">
+        <x:v>Player3D / bunny01 v006 / 两套9m楼梯 / 楼顶洞口与镜头</x:v>
+      </x:c>
+      <x:c r="E30" s="70" t="str">
+        <x:v>六态扩展为八态falling/landing；1.5m玩法碰撞改胶囊；楼梯取消Y吸附并合并连续三角承重面；掉落/钥匙向下找承重面；导入墙补同形碰撞；楼顶洞口收紧、8m镜头侧向避障并加物理天空反弹光；进入特殊楼梯围护体立即启用角色探照灯。</x:v>
+      </x:c>
+      <x:c r="F30" s="70" t="str">
+        <x:v>不新增角色/楼梯AssetID、GLB或贴图；v006模型尺寸和单太阳参数不变；原战斗/命运/枪械/流送兼容。</x:v>
+      </x:c>
+      <x:c r="G30" s="70" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" ht="118" customHeight="1">
+      <x:c r="A31" s="70" t="str">
+        <x:v>v1.25</x:v>
+      </x:c>
+      <x:c r="B31" s="71" t="n">
+        <x:v>46233</x:v>
+      </x:c>
+      <x:c r="C31" s="70" t="str">
+        <x:v>PH43楼梯Walkable根因修复与固定镜头</x:v>
+      </x:c>
+      <x:c r="D31" s="70" t="str">
+        <x:v>Player3D / bunny01 v006 / 两套9m楼梯 / 楼顶洞口与镜头</x:v>
+      </x:c>
+      <x:c r="E31" s="70" t="str">
+        <x:v>六态扩展为八态falling/landing；1.5m玩法碰撞改胶囊；楼梯取消Y吸附与程序路径承重面，直接采用v006每套六块*Walkable网格同形常驻碰撞；掉落/钥匙向下找承重面；EnclosureWall补围护碰撞；楼顶洞口收紧并加物理天空反弹光；镜头固定(0,8,5.5)、FOV 55°，每物理帧覆盖外部位移与旋转；进入特殊楼梯围护体立即启用角色探照灯。</x:v>
+      </x:c>
+      <x:c r="F31" s="70" t="str">
+        <x:v>不新增角色/楼梯AssetID、GLB或贴图；v006模型尺寸和单太阳参数不变；原战斗/命运/枪械/流送兼容。</x:v>
+      </x:c>
+      <x:c r="G31" s="70" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" ht="118" customHeight="1">
+      <x:c r="A32" s="70" t="str">
+        <x:v>v1.26</x:v>
+      </x:c>
+      <x:c r="B32" s="71" t="n">
+        <x:v>46233</x:v>
+      </x:c>
+      <x:c r="C32" s="70" t="str">
+        <x:v>PH44二百五十米塔楼与四乘四战斗层重构</x:v>
+      </x:c>
+      <x:c r="D32" s="70" t="str">
+        <x:v>塔楼整层 / 5m地砖与墙体 / 两套9m楼梯 / 固定镜头局部剖切</x:v>
+      </x:c>
+      <x:c r="E32" s="70" t="str">
+        <x:v>整层统一50×50格（250×250m、2500砖）；65×65m基地核心不变并偏移2.5m对齐；普通层12个45×45m房间，Boss层90×90m Boss区+9个普通房；实墙按方向MultiMesh批渲染并合并碰撞；上下楼梯分别记录两端门侧；固定8m镜头只剖切挡住角色的墙体渲染；楼顶天空反弹光降至1.25。</x:v>
+      </x:c>
+      <x:c r="F32" s="70" t="str">
+        <x:v>不新增AssetID、GLB或贴图；v006楼梯与既有5m模块继续复用；碰撞、房门、命运卡、刷怪、流送和固定镜头角度保持兼容。完整探索节点数2783。</x:v>
+      </x:c>
+      <x:c r="G32" s="70" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:G2"/>
